--- a/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/_tutorial.xlsx
@@ -484,9 +484,9 @@
           <t xml:space="preserve">A Journey Begins </t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O Início da Aventura</t>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uma jornada começa </t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Como Usar as Ferramentas</t>
+          <t>Usando ferramentas</t>
         </is>
       </c>
       <c r="I6" s="15" t="n"/>
@@ -561,9 +561,9 @@
           <t>Very Important Stuff</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Algo Muito Importante</t>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Coisas muito importantes</t>
         </is>
       </c>
     </row>
@@ -596,9 +596,9 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>A Importância dos Equipamentos</t>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Equipamento</t>
         </is>
       </c>
     </row>
@@ -631,9 +631,9 @@
           <t>Food</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Situação dos Alimentos</t>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Comida</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Materiais Processados</t>
+          <t>Recurso processado</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>Dureza dos Materiais</t>
+          <t>Dureza do material</t>
         </is>
       </c>
     </row>
@@ -736,9 +736,9 @@
           <t>Sleep and Rest</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sono e Descanso</t>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Sono e descanso</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Características dos Itens</t>
+          <t>Traço de item</t>
         </is>
       </c>
       <c r="I13" s="15" t="n"/>
@@ -813,9 +813,9 @@
           <t>Global Map</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mapa Global</t>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Mapa global</t>
         </is>
       </c>
     </row>
@@ -848,9 +848,9 @@
           <t>Growth and Feat</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Crescimento e Talentos</t>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Crescimento e Dotes</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
           <t>Fame</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Fama</t>
         </is>
@@ -918,9 +918,9 @@
           <t>Karma</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Carma</t>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Karma</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
           <t>Criminal</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>Criminoso</t>
         </is>
@@ -988,9 +988,9 @@
           <t>Weakness and Restoration</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Enfraquecimento e Recuperação</t>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Fraqueza e restauração</t>
         </is>
       </c>
     </row>
@@ -1023,9 +1023,9 @@
           <t>Acid Damage to Equipment</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Deterioração dos Equipamentos por Ácido</t>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Dano de ácido ao equipamento</t>
         </is>
       </c>
     </row>
@@ -1058,9 +1058,9 @@
           <t>Faith and Praying</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Fé e Orações</t>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Fé e oração</t>
         </is>
       </c>
     </row>
@@ -1093,9 +1093,9 @@
           <t>Death and Penalty</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Morte e Consequências</t>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Morte e penalidade</t>
         </is>
       </c>
     </row>
@@ -1128,9 +1128,9 @@
           <t>Reviving Pets and Residents</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Ressurreição de Companheiros e Moradores</t>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Revivendo bichos e moradores</t>
         </is>
       </c>
     </row>
@@ -1163,9 +1163,9 @@
           <t>Childhood's End</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Fim da Infância</t>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>O fim da infância</t>
         </is>
       </c>
     </row>
@@ -1198,9 +1198,9 @@
           <t>Dangerous Water</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Água Perigosa</t>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Água perigosa</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
           <t>Field Effect</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="15" t="inlineStr">
         <is>
           <t>Efeito de Campo</t>
         </is>
@@ -1268,9 +1268,9 @@
           <t>Ether Disease</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Doença do Éter</t>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Doença de Éter</t>
         </is>
       </c>
     </row>
@@ -1303,9 +1303,9 @@
           <t>Tinker's Camp</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Ponto de Parada do Mercador Viajante</t>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Acampamento dos Latoeiros</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Cidade</t>
+          <t>Cidades</t>
         </is>
       </c>
       <c r="I29" s="15" t="n"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Grau de Influência</t>
+          <t>Influência</t>
         </is>
       </c>
       <c r="I30" s="15" t="n"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Caixa de Entregas</t>
+          <t>Caixa de entregas</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Pedra da Cidade</t>
+          <t>Pedra do Lar</t>
         </is>
       </c>
       <c r="I32" s="15" t="n"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Trabalhos e Hobbies dos Moradores</t>
+          <t>Trabalho e hobbies</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Pasto e Gado</t>
+          <t>Pasto e gado</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Problema com o Lixo</t>
+          <t>Problema do lixo</t>
         </is>
       </c>
       <c r="I35" s="15" t="n"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Estações do Ano</t>
+          <t>Estações</t>
         </is>
       </c>
       <c r="I36" s="15" t="n"/>
@@ -1661,9 +1661,9 @@
           <t>Nerun demo</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Nerun Demo</t>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Demo da Nerun</t>
         </is>
       </c>
     </row>
@@ -1696,9 +1696,9 @@
           <t>Winter Warning</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Alerta de Inverno</t>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Aviso de inverno</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
           <t>The Hour of Ragnarok</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
         <is>
           <t>A Hora do Ragnarok</t>
         </is>
@@ -1750,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K373"/>
+  <dimension ref="A1:K374"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.83" customWidth="1" style="15" min="1" max="3"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="K12" s="15" t="n"/>
     </row>
-    <row r="13" ht="35.05" customHeight="1" s="17">
+    <row r="13" ht="12.8" customHeight="1" s="17">
       <c r="I13" s="19" t="inlineStr">
         <is>
           <t>…</t>
@@ -1899,11 +1899,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
+      <c r="K13" s="15" t="n"/>
     </row>
     <row r="14" ht="22.35" customHeight="1" s="17">
       <c r="H14" s="15" t="n">
@@ -1923,8 +1919,8 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>Está sentindo?
-Esse ar estranho... há uma lei especial agindo aqui.</t>
+          <t>Sente?
+Este ar estranho... há uma lei especial em ação aqui.</t>
         </is>
       </c>
     </row>
@@ -1946,8 +1942,8 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Sim—algo como um ‘Efeito de Campo’ está pulsando neste lugar.
-Já ouvi falar disso antes, mas esta é a primeira vez que sinto na pele.</t>
+          <t>Sim: algo como um 'Efeito de Campo' pulsa neste lugar.
+Já ouvi falar disso, mas é a primeira vez que eu mesma experimento.</t>
         </is>
       </c>
     </row>
@@ -1971,9 +1967,9 @@
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Um Efeito de Campo é uma regra especial que se aplica apenas ao mapa em que você está.
+          <t>Um Efeito de Campo é uma regra especial que vale só para o mapa em que você está.
 Vê aquele ícone desconhecido à direita do relógio?
-Se verificar, pode descobrir qual efeito está ativo.</t>
+Se checá-lo, você aprende qual efeito está ativo.</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1991,12 @@
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Há um poder aqui forte o suficiente para distorcer as próprias leis do mundo.
-E, claro, deve haver uma razão para isso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22.35" customHeight="1" s="17">
+          <t>Há um poder aqui forte o bastante para dobrar as próprias leis do mundo.
+E, claro, deve haver um motivo para isso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="12.8" customHeight="1" s="17">
       <c r="H18" s="15" t="n">
         <v>327</v>
       </c>
@@ -2068,8 +2064,8 @@
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>Tlim-tlim!
-Você acredita nisso?
+          <t>Tilintim!
+Acredita?
 Já se passaram dois mil anos desde que você começou sua aventura!</t>
         </is>
       </c>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="K25" s="15" t="inlineStr">
         <is>
-          <t>Você vive bastante, hein?</t>
+          <t>Você é dos longevos, hein?</t>
         </is>
       </c>
     </row>
@@ -2135,8 +2131,8 @@
       <c r="K26" s="15" t="inlineStr">
         <is>
           <t>Eu?
-... Que grosseria. Ainda sou uma jovenzinha fada cheia de energia, é claro.
-Fadas são assim mesmo.</t>
+...Que grosseria. Continuo uma jovem fada cheia de pique, claro.
+Fadas são assim.</t>
         </is>
       </c>
     </row>
@@ -2160,9 +2156,9 @@
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Mas ai, ai!
-Este mundo não vai durar para sempre.
-O fim se aproxima, suavemente, mas com certeza.</t>
+          <t>Mas, ai de mim!
+Este mundo não durará para sempre.
+O fim se aproxima, suave mas certamente.</t>
         </is>
       </c>
     </row>
@@ -2189,9 +2185,9 @@
       <c r="K28" s="15" t="inlineStr">
         <is>
           <t>A Hora do Ragnarok...
-Nem eu sei exatamente o que isso significa.
-Mas dizem que, quando o mundo ultrapassa quatro mil anos,
-ele começa a se desfazer — fenômenos estranhos começam a surgir.</t>
+Até eu não sei exatamente o que isso significa.
+Mas dizem que quando o mundo ultrapassa quatro mil anos,
+ele começa a se desfazer: fenômenos estranhos começam a aparecer.</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2208,7 @@
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>Infelizmente, ainda não foi encontrada uma forma de impedir esse desmoronamento.</t>
+          <t>Tristemente, ainda não se encontrou um jeito de impedir esse desfazer.</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2248,7 @@
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Quero continuar aventurando com você pra sempre…</t>
+          <t>Eu queria continuar aventurando com você para sempre...</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2271,7 @@
       <c r="K32" s="15" t="inlineStr">
         <is>
           <t>Então...
-Que tal diminuirmos um pouquinho o ritmo daqui pra frente?</t>
+Que tal desacelerarmos um pouquinho daqui para frente?</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2309,7 @@
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>Olha, uma erva!</t>
+          <t>Olhe, uma erva!</t>
         </is>
       </c>
     </row>
@@ -2337,8 +2333,9 @@
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>Às vezes, há plantas coloridas que crescem na natureza.
-Elas são chamadas de ervas medicinais ou, às vezes, apenas “ervas” e são realmente boas para a saúde se você as consumir.</t>
+          <t>Às vezes há plantas coloridas crescendo na natureza.
+São as ervas medicinais, ou simplesmente 'ervas',
+e fazem muito bem à saúde se você as comer.</t>
         </is>
       </c>
     </row>
@@ -2362,8 +2359,9 @@
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
-          <t>É claro que elas também podem ser usadas como tempero. 
-Se você moê-las em pó usando um “pilão”, elas também podem se tornar ingredientes para todos os tipos de medicamentos.</t>
+          <t>Claro, elas também servem de tempero.
+Se você moer até virar pó num 'pilão',
+elas viram ingrediente de todo tipo de remédio.</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2383,8 @@
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>Por que você não abre sua mochila e dá uma olhada na erva que acabou de colher?</t>
+          <t>Por que não abre a mochila e
+dá uma olhada na erva que acabou de colher?</t>
         </is>
       </c>
     </row>
@@ -2409,8 +2408,9 @@
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Você verá efeitos listados entre colchetes, como【Hemostático】.
-Esses efeitos são chamados de “Características do Item” e, quando você cria algo com eles, essas características são transferidas para o produto final.</t>
+          <t>Você vai ver efeitos entre colchetes, tipo 【Hemostática】.
+São os 'traços de item': quando você fabrica com elas,
+essas características passam para o produto pronto.</t>
         </is>
       </c>
     </row>
@@ -2432,8 +2432,8 @@
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Por exemplo, se você fizer um curativo com ervas que tenham efeito hemostático ou antiveneno... 
-Acho que você entendeu a ideia.</t>
+          <t>Por exemplo, se você fizer uma bandagem usando uma erva hemostática ou antídoto como ingrediente...
+Exatamente, você pegou a ideia.</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,9 @@
       </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
-          <t>Eu gostaria de coletar ervas de cores diferentes, porque ervas diferentes têm efeitos diferentes dependendo da cor da grama.</t>
+          <t>Cada cor de erva tem efeitos diferentes,
+então vale colecionar um arco-íris inteiro delas.
+Colorido em mais de um sentido...</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2478,7 @@
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>Entendeu? Color-idas!</t>
+          <t>Entendeu? Co...lorido!</t>
         </is>
       </c>
     </row>
@@ -2542,8 +2544,8 @@
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>Tinkle-tinkle!_x000D_
-Inverno... o inverno está chegando!</t>
+          <t>Tilintim!
+O inverno... o inverno está chegando!</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2565,7 @@
       </c>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>Certifique-se de terminar a colheita das plantações no campo.</t>
+          <t>Não se esqueça de terminar de colher as plantações do campo.</t>
         </is>
       </c>
     </row>
@@ -2616,10 +2618,10 @@
 Time really flies!</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Já estamos no outono...
-O tempo realmente voa!</t>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>Já é outono...
+O tempo voa!</t>
         </is>
       </c>
     </row>
@@ -2641,9 +2643,11 @@
 it’s never so hot that you can’t go outside.</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Como Tyris do Norte é um continente mais ao norte, mesmo durante o verão quente, quando o sol bate forte, nunca está tão quente que você não possa sair de casa.</t>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>Como Tyris do Norte é um continente ao norte,
+mesmo no verão escaldante, quando o sol bate forte,
+nunca é calor demais para sair.</t>
         </is>
       </c>
     </row>
@@ -2663,10 +2667,10 @@
 It might be a good idea to start preparing for it now.</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>No entanto, o inverno tem seu próprio impacto na vida cotidiana.
-Pode ser uma boa ideia começar a se preparar para ele agora.</t>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>Mas o inverno tem seu impacto no dia a dia.
+Talvez seja bom começar a se preparar agora.</t>
         </is>
       </c>
     </row>
@@ -2687,10 +2691,10 @@
 So, make sure to harvest them before then, okay?</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Se você estiver com alguma plantação, ela murchará com a chegada do inverno.
-Portanto, certifique-se de colhê-las antes disso, ok?</t>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>Se você está cultivando plantações, elas murcham quando o inverno chega.
+Então colha antes disso, combinado?</t>
         </is>
       </c>
     </row>
@@ -2711,10 +2715,11 @@
 Be careful about that if you make a living through fishing,</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>E quando os lagos e mares congelarem, é claro, você não poderá mais pescar.
-Tenha cuidado com isso se você vive da pesca,</t>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>E quando os lagos e mares congelam,
+claro, não dá mais para pescar.
+Cuidado com isso se você vive da pesca.</t>
         </is>
       </c>
     </row>
@@ -2738,9 +2743,12 @@
 so you have to go check it out! Got it!?</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Ah, e em dezembro, há um famoso festival em um vilarejo chamado Noyel, a leste. Eles vendem doces realmente deliciosos nas barracas, então você tem que ir lá conferir! Entendeu?</t>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>Ah, e em dezembro tem um festival famoso
+numa vila chamada Noyel, a leste.
+Eles vendem doces deliciosos nas barraquinhas,
+então você tem de ir ver! Combinado!?</t>
         </is>
       </c>
     </row>
@@ -2760,10 +2768,10 @@
 If you have the time, it might be fun to visit them. </t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Há festivais em diferentes partes do país em todas as estações, não apenas no inverno.
-Dê uma olhada quando tiver tempo.</t>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Além do inverno, há festivais pela terra toda a cada estação.
+Se sobrar tempo, pode ser divertido visitá-los. </t>
         </is>
       </c>
     </row>
@@ -2811,9 +2819,9 @@
           <t>...Want to know how to use the axe?</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Você quer saber como usar um machado?</t>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>...Quer saber como usar o machado?</t>
         </is>
       </c>
     </row>
@@ -2835,11 +2843,11 @@
 Once you're holding the axe, right-click on a tree on the ground, and you'll be able to chop it down.</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Se você clicar no ícone da bolsa na tela, ele mostrará seu inventário, certo?
-A partir daí, encontre o machado e clique com o botão direito do mouse nele para equipá-lo.
-Quando estiver segurando o machado, clique com o botão direito do mouse em uma árvore no chão e você poderá cortá-la.</t>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>Se você clicar no ícone da mochila na tela, ela mostra seu inventário, certo?
+De lá, ache o machado e clique com o botão direito para equipá-lo.
+Com o machado na mão, clique com o botão direito numa árvore no chão, e você poderá derrubá-la.</t>
         </is>
       </c>
     </row>
@@ -2857,9 +2865,9 @@
           <t>...Huh? You already knew that?</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>... Hã? Você sabia disso?</t>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>...Hã? Você já sabia disso?</t>
         </is>
       </c>
     </row>
@@ -2879,10 +2887,10 @@
 Don't worry about it... Everyone starts out as a beginner.</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>...Hehe... Bem, bem..._x000D_
-Não se preocupe com isso... Todo mundo começa como iniciante.</t>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>...Hehe... Bom, bom...
+Não se preocupe... Todo mundo começa como iniciante.</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2908,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="15" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2925,12 +2933,12 @@
 It's really convenient.</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>A propósito, está vendo os espaços numerados na parte inferior direita da tela?
-Se você arrastar e soltar o machado em um desses espaços,
-poderá alternar facilmente entre as ferramentas usando a roda do mouse.
-É muito conveniente.</t>
+      <c r="K71" s="15" t="inlineStr">
+        <is>
+          <t>Aliás, você vê os slots numerados no canto inferior direito da tela?
+Se arrastar e soltar o machado num deles,
+você troca de ferramenta fácil com a rodinha do mouse.
+É muito prático.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2956,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="15" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2970,10 +2978,10 @@
 I thought so, but just in case...just in case, right?</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>... E-eé... Acho que você já sabia disso também!
-Eu imaginei, mas só por precaução, né?</t>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>...S-sim... Acho que você sabia disso também!
+Eu imaginava, mas por precaução... por precaução, né?</t>
         </is>
       </c>
     </row>
@@ -2991,9 +2999,9 @@
           <t>Well then...</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Vejamos…</t>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>Pois então...</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3048,7 @@
           <t>Hey, have you ever heard of influence?</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="15" t="inlineStr">
         <is>
           <t>Ei, você já ouviu falar de influência?</t>
         </is>
@@ -3062,9 +3070,10 @@
 your 'influence' in that town increases.</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Quando você completa missões, investe ou contribui com uma cidade, sua “influência” nessa cidade aumenta.</t>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>Quando você completa missões, investe ou contribui com uma cidade,
+sua 'influência' naquela cidade aumenta.</t>
         </is>
       </c>
     </row>
@@ -3086,9 +3095,11 @@
 and even ask for some pretty impossible favors.</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>À medida que sua influência aumenta, você poderá atualizar a lista de missões disponíveis, fazer com que as lojas reabasteçam seus estoques no local e até mesmo pedir alguns favores impossíveis.</t>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>Conforme a influência sobe, você pode renovar a lista de missões disponíveis,
+mandar as lojas reabastecerem o estoque na hora,
+e até pedir alguns favores bem impossíveis.</t>
         </is>
       </c>
     </row>
@@ -3106,9 +3117,9 @@
           <t>...And that’s not all!</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>... E não é só isso!</t>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>...E não é só isso!</t>
         </is>
       </c>
     </row>
@@ -3130,11 +3141,11 @@
 sold by the town's secretary.</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Você também pode usar influência como moeda._x000D_
-Por exemplo, um dos itens de troca mais populares é o 'Ticket de Mobiliário'_x000D_
-vendido pelo secretário da cidade.</t>
+      <c r="K84" s="15" t="inlineStr">
+        <is>
+          <t>Você pode até usar influência como moeda.
+Por exemplo, um dos itens de troca populares é o 'Vale Mobília'
+vendido pela secretária da cidade.</t>
         </is>
       </c>
     </row>
@@ -3154,10 +3165,10 @@
 It’s handy if you’re trying to collect furniture that’s only available in certain towns.</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Você pode usar esse tíquete para confiscar à força os móveis colocados na cidade.
-É útil se você estiver tentando coletar móveis que só estão disponíveis em determinadas cidades.</t>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>Com este vale, você pode confiscar à força móveis colocados na cidade.
+É útil se você está atrás de móveis que só existem em certas cidades.</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3207,7 @@
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Olha! Tem uma caixa de entregas aqui.</t>
+          <t>Olhe! Tem uma caixa de entregas aqui.</t>
         </is>
       </c>
     </row>
@@ -3220,9 +3231,9 @@
       </c>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Carregar muitos itens está deixando você lento...
-Mas você não quer desperdiçar nada simplesmente o jogando fora...
-A caixa de entrega é um serviço útil que resolve esse problema comum dos aventureiros.</t>
+          <t>Carregar itens demais está te deixando lento...
+Mas você não quer desperdiçar nada jogando fora...
+A caixa de entregas é um serviço prático que resolve esse problema clássico de aventureiro.</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3255,8 @@
       </c>
       <c r="K92" s="15" t="inlineStr">
         <is>
-          <t>Se você colocar seus itens nessa caixa, eles serão entregues automaticamente na próxima base que você visitar.</t>
+          <t>Se você puser seus itens nesta caixa,
+eles são entregues automaticamente na próxima base que você visitar.</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3280,9 @@
       </c>
       <c r="K93" s="15" t="inlineStr">
         <is>
-          <t>Você pode usá-lo para enviar móveis pesados que comprou na cidade ou para mover itens entre suas bases. É muito conveniente quando você pega o jeito.</t>
+          <t>Dá para usar para mandar móveis pesados comprados na cidade ou
+para mover itens entre suas bases.
+Fica muito prático depois que você pega o jeito.</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3316,7 @@
           <t>Good morning, sleepyhead.</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K99" s="15" t="inlineStr">
         <is>
           <t>Bom dia, dorminhoco.</t>
         </is>
@@ -3325,10 +3339,10 @@
 I'm Nerun, your guide here to assist you on your journey.</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>... Não se preocupe, você não está tendo alucinações. 
-Sou Nerun, seu guia, e estou aqui para ajudá-lo em sua jornada.</t>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>...Fique tranquilo, você não está alucinando.
+Eu sou a Nerun, sua guia, aqui para ajudar você na jornada.</t>
         </is>
       </c>
     </row>
@@ -3350,10 +3364,11 @@
 A handy tool that lets you replay our conversations anytime you want.</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Bem, parece que você acabou de acordar, então, por hoje, vou lhe dar este “Registro de Aventuras”.
-Uma ferramenta útil que permite que você repita essas conversas sempre que quiser.</t>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>Bem, você parece que acabou de acordar, então hoje
+só vou te dar este "Diário de Aventura".
+Uma ferramenta prática para rever nossas conversas quando quiser.</t>
         </is>
       </c>
     </row>
@@ -3371,9 +3386,9 @@
           <t xml:space="preserve">Well, until we meet again then... </t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Bem, estamos ansiosos para trabalhar com você no futuro...</t>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pois então... até a próxima... </t>
         </is>
       </c>
     </row>
@@ -3454,7 +3469,7 @@
       </c>
       <c r="K107" s="19" t="inlineStr">
         <is>
-          <t>Ah, não, seu equipamento enferrujou por ter sido exposto a ácido…</t>
+          <t>Ai não, seu equipamento enferrujou por exposição ao ácido...</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3498,8 @@
       </c>
       <c r="K108" s="19" t="inlineStr">
         <is>
-          <t>Quando o equipamento fica enferrujado, suas estatísticas diminuem em -1, -2 e assim por diante, fazendo com que ele seja menos eficaz.</t>
+          <t>Quando o equipamento enferruja, os status dele caem em -1, -2 e por aí vai,
+e ele fica menos eficaz.</t>
         </is>
       </c>
     </row>
@@ -3516,8 +3532,10 @@
       </c>
       <c r="K109" s="19" t="inlineStr">
         <is>
-          <t>Neste mundo, há muitas criaturas desagradáveis que o encharcarão de ácido só de tocar, espalharão doenças estranhas e destruirão seu equipamento, portanto, tenha cuidado.
-... Lembre-se, aprender com a experiência e com o fracasso é o que faz um verdadeiro aventureiro!</t>
+          <t>Neste mundo, há muitas criaturas desagradáveis que
+jogam ácido em você só de tocar, espalham doenças estranhas
+e destroem seu equipamento, então cuidado.
+...Lembre: aprender com a experiência e o fracasso é o que faz um verdadeiro aventureiro!</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3566,9 @@
       </c>
       <c r="K110" s="19" t="inlineStr">
         <is>
-          <t>... A propósito, mesmo que seu equipamento se torne inútil devido à ferrugem, você ainda pode restaurá-lo com uma Pedra de amolar. Talvez você deva guardá-lo em vez de jogá-lo fora?</t>
+          <t>...Aliás, mesmo que seu equipamento fique inútil pela ferrugem,
+você ainda pode restaurá-lo com uma pedra de amolar.
+Talvez seja melhor guardar em vez de jogar fora?</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3639,7 @@
       </c>
       <c r="K114" s="19" t="inlineStr">
         <is>
-          <t>Aqui está uma lista dos moradores da sua base.</t>
+          <t>Aqui está a lista de moradores da sua base.</t>
         </is>
       </c>
     </row>
@@ -3648,8 +3668,8 @@
       </c>
       <c r="K115" s="19" t="inlineStr">
         <is>
-          <t>Está vendo o ícone da pasta ao lado dos nomes deles?
-Se passar o mouse sobre ele, poderá ver seus hobbies e empregos.</t>
+          <t>Vê o ícone de maleta ao lado dos nomes?
+Se você pousar o mouse sobre ele, vê os hobbies e trabalhos deles.</t>
         </is>
       </c>
     </row>
@@ -3680,9 +3700,9 @@
       </c>
       <c r="K116" s="19" t="inlineStr">
         <is>
-          <t>Os moradores têm várias funções._x000D_
-Alguns melhoram a segurança ou a fertilidade da sua base,_x000D_
-enquanto outros produzem itens valiosos.</t>
+          <t>Moradores têm vários trabalhos.
+Alguns melhoram a segurança ou a fertilidade da sua base,
+outros produzem itens valiosos.</t>
         </is>
       </c>
     </row>
@@ -3711,9 +3731,8 @@
       </c>
       <c r="K117" s="19" t="inlineStr">
         <is>
-          <t>Esteja ciente de que os residentes não farão o trabalho se o respectivo ambiente não estiver pronto.
-Os trabalhos com nomes em amarelo são aqueles que não são viáveis no momento.
-Enquanto outros produzem itens valiosos.</t>
+          <t>Porém, se o ambiente não estiver certo, os moradores não trabalham.
+Trabalhos mostrados em amarelo estão impossíveis de executar agora.</t>
         </is>
       </c>
     </row>
@@ -3744,8 +3763,9 @@
       </c>
       <c r="K118" s="19" t="inlineStr">
         <is>
-          <t>Normalmente, se você colocar os móveis certos para o trabalho em sua base, eles começarão a trabalhar.
-Por exemplo, uma estante de livros é necessária para trabalhos de pesquisa.</t>
+          <t>Normalmente, se você colocar o móvel certo para o trabalho na base,
+eles começam a trabalhar.
+Por exemplo, uma estante é necessária para trabalhos de pesquisa.</t>
         </is>
       </c>
     </row>
@@ -3775,9 +3795,9 @@
       </c>
       <c r="K119" s="19" t="inlineStr">
         <is>
-          <t>À medida que os habitantes aumentam, a eficiência do trabalho também aumenta.
-A qualidade de suas camas também afeta a eficiência,
-portanto, é uma boa ideia ter uma cama para cada residente.</t>
+          <t>A eficiência do trabalho deles aumenta conforme os moradores crescem.
+A qualidade das camas também afeta a eficiência,
+então é bom ter uma cama para cada morador.</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3885,8 @@
       </c>
       <c r="K123" s="19" t="inlineStr">
         <is>
-          <t>Essa grama que cresce em toda parte é um bom alimento para o gado.</t>
+          <t>Esta grama cresce em todo lugar,
+mas é, na verdade, um ótimo pasto para o gado.</t>
         </is>
       </c>
     </row>
@@ -3896,8 +3917,9 @@
       </c>
       <c r="K124" s="19" t="inlineStr">
         <is>
-          <t>Se você colocar a grama no chão ou em um recipiente compartilhado, os animais a comerão por conta própria todos os dias.
-E os animais que consomem grama podem, às vezes, produzir ovos ou leite.</t>
+          <t>Se você puser a grama no chão ou num contêiner compartilhado,
+o gado da sua base come dela todo dia.
+E às vezes, o gado que come a grama produz ovos ou leite.</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3948,8 @@
       </c>
       <c r="K125" s="19" t="inlineStr">
         <is>
-          <t>Por que você não leva as sementes para a sua casa e as cultiva em sua base?</t>
+          <t>Ah, por que você não leva umas sementes
+para tentar cultivar na sua base?</t>
         </is>
       </c>
     </row>
@@ -3985,7 +4008,7 @@
       </c>
       <c r="K128" s="19" t="inlineStr">
         <is>
-          <t>Isso é água.</t>
+          <t>Isto é água.</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4063,8 @@
       </c>
       <c r="K130" s="19" t="inlineStr">
         <is>
-          <t>Você fez uma cara de "que coisa óbvia para se dizer", não foi?</t>
+          <t>Você acabou de fazer uma cara de
+"que obviedade", não fez?</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4093,8 @@
       </c>
       <c r="K131" s="19" t="inlineStr">
         <is>
-          <t>... Tudo bem, você deve aprender por experiência própria como as águas profundas podem ser aterrorizantes. Você vai se sufocar e morrer rapidamente. E não diga que eu não o avisei!</t>
+          <t>...Tudo bem, você vai aprender na prática o quão aterrorizante é a água funda.
+Você se afoga e morre rapidinho. Eu avisei!</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4155,8 @@
       </c>
       <c r="K134" s="19" t="inlineStr">
         <is>
-          <t>Meu Deus #pc, como você pôde morrer tão facilmente…</t>
+          <t>Ai, #pc...
+como você consegue morrer tão fácil...</t>
         </is>
       </c>
     </row>
@@ -4161,9 +4187,9 @@
       </c>
       <c r="K135" s="19" t="inlineStr">
         <is>
-          <t>Como diabos você morreu?
-Bem, não se preocupe. 
-Eu o trarei de volta à vida sempre que puder!</t>
+          <t>Como você conseguiu morrer, afinal?
+Mas não se preocupe,
+eu te trago de volta à vida quantas vezes precisar.</t>
         </is>
       </c>
     </row>
@@ -4195,8 +4221,9 @@
       </c>
       <c r="K136" s="19" t="inlineStr">
         <is>
-          <t>É claro que morrer tem um preço.
-Você pode perder parte do seu ouro no local e suas estatísticas podem diminuir, portanto, é melhor evitar se for possível.</t>
+          <t>Claro, morrer tem um preço.
+Você pode deixar cair um pouco do seu ouro na hora,
+e seus status podem diminuir, então o melhor é evitar se puder.</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4253,8 @@
       </c>
       <c r="K137" s="19" t="inlineStr">
         <is>
-          <t>No entanto, nos primeiros 90 dias após sua chegada a esta terra, você não sofrerá nenhuma penalidade por morrer.</t>
+          <t>Porém, nos primeiros 90 dias depois de chegar nesta terra,
+você não sofre nenhuma penalidade por morrer.</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4283,8 @@
       </c>
       <c r="K138" s="19" t="inlineStr">
         <is>
-          <t>Portanto, sinta-se à vontade para enfrentar todos os tipos de desafios e aprender com a experiência. Hehe.</t>
+          <t>Então, fique à vontade para encarar todo tipo de desafio
+e aprender na prática. Hehe.</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4355,7 @@
       </c>
       <c r="K142" s="19" t="inlineStr">
         <is>
-          <t>Seu companheiro está morto...</t>
+          <t>Ai não, você perdeu um companheiro...</t>
         </is>
       </c>
     </row>
@@ -4357,8 +4386,9 @@
       </c>
       <c r="K143" s="19" t="inlineStr">
         <is>
-          <t>Calma, calma, não fique muito triste.
-Seu companheiro provavelmente voltará à vida após uma semana ou um pouco mais.</t>
+          <t>Vem cá, não fique triste demais.
+Seu companheiro provavelmente volta à vida tranquilo
+depois de uma semana mais ou menos.</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4419,9 @@
       </c>
       <c r="K144" s="19" t="inlineStr">
         <is>
-          <t>Quando um companheiro morre, ele sai temporariamente de seu grupo e é enviado de volta à base à qual pertence. Portanto, volte para a base para checar se ele está lá depois de algum tempo.</t>
+          <t>Quando um companheiro morre, ele deixa temporariamente o seu grupo
+e é mandado de volta para a base a que pertence.
+Então confira a base depois de um tempo.</t>
         </is>
       </c>
     </row>
@@ -4418,8 +4450,8 @@
       </c>
       <c r="K145" s="19" t="inlineStr">
         <is>
-          <t>Se não puder esperar, você também pode falar com os barmen em várias cidades.
-Isso custará algum dinheiro, mas eles podem trazer seu companheiro de volta imediatamente.</t>
+          <t>Se você não aguenta esperar, também pode falar com os barmen de várias cidades.
+Custa algum dinheiro, mas eles trazem seu companheiro de volta na hora.</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4480,8 @@
       </c>
       <c r="K146" s="19" t="inlineStr">
         <is>
-          <t>E se for um animal de estimação que você ganhou daquela garota... Fiama, você pode falar com ela a qualquer momento para revivê-lo.</t>
+          <t>E se for um bicho que você ganhou daquela garota... a Fiama,
+você pode falar com ela a qualquer hora para revivê-lo.</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4509,8 @@
       </c>
       <c r="K147" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eu sei que é difícil, mas aguente firme... </t>
+          <t>Sei que você está triste agora,
+mas aguente firme...</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4595,7 @@
       </c>
       <c r="K152" s="19" t="inlineStr">
         <is>
-          <t>Tlim-tlim!
+          <t>Tilintim!
 Seu período de aventureiro iniciante acabou!</t>
         </is>
       </c>
@@ -4595,46 +4629,36 @@
       </c>
       <c r="K153" s="19" t="inlineStr">
         <is>
-          <t>Ah, você não morreu nenhuma vez, né?
-Ótimo, ótimo. Venha aqui, deixa eu fazer uns cafunés!</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>Oh, você não morreu nenhuma vez, hein?
+Boa, boa. Vem cá, deixa te fazer cafuné!</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="A154" s="19" t="n"/>
       <c r="B154" s="19" t="n"/>
       <c r="C154" s="19" t="inlineStr">
         <is>
-          <t>nerun_nadenade2</t>
-        </is>
-      </c>
-      <c r="D154" s="19" t="n"/>
-      <c r="E154" s="19" t="n"/>
+          <t>nerun_nadenade</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>getAchievement</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
+        <is>
+          <t>NERUN2</t>
+        </is>
+      </c>
       <c r="F154" s="19" t="n"/>
       <c r="G154" s="19" t="n"/>
-      <c r="H154" s="15" t="n">
-        <v>231</v>
-      </c>
-      <c r="I154" s="26" t="inlineStr">
-        <is>
-          <t>この期間にキミが死んだ回数は実に#1回…
-一体、何をしていたの？</t>
-        </is>
-      </c>
-      <c r="J154" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The number of times you died during this period is actually #1...
-What on earth were you doing? </t>
-        </is>
-      </c>
-      <c r="K154" s="19" t="inlineStr">
-        <is>
-          <t>O número de vezes que você morreu durante este período é, na verdade, #1...
-O que diabos você estava fazendo?</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="I154" s="26" t="n"/>
+      <c r="J154" s="25" t="n"/>
+      <c r="K154" s="19" t="n"/>
+    </row>
+    <row r="155" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A155" s="19" t="n"/>
       <c r="B155" s="19" t="n"/>
       <c r="C155" s="19" t="inlineStr">
@@ -4647,55 +4671,59 @@
       <c r="F155" s="19" t="n"/>
       <c r="G155" s="19" t="n"/>
       <c r="H155" s="15" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I155" s="26" t="inlineStr">
         <is>
-          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
+          <t>この期間にキミが死んだ回数は実に#1回…
+一体、何をしていたの？</t>
         </is>
       </c>
       <c r="J155" s="25" t="inlineStr">
         <is>
-          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
+          <t xml:space="preserve">The number of times you died during this period is actually #1...
+What on earth were you doing? </t>
         </is>
       </c>
       <c r="K155" s="19" t="inlineStr">
         <is>
-          <t>Até para mim, nunca vi um aventureiro como você...</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t xml:space="preserve">O número de vezes que você morreu neste período foi #1...
+O que você andou fazendo, criatura? </t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="22.35" customFormat="1" customHeight="1" s="15">
       <c r="A156" s="19" t="n"/>
       <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="n"/>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>nerun_nadenade2</t>
+        </is>
+      </c>
       <c r="D156" s="19" t="n"/>
       <c r="E156" s="19" t="n"/>
       <c r="F156" s="19" t="n"/>
       <c r="G156" s="19" t="n"/>
       <c r="H156" s="15" t="n">
-        <v>128</v>
-      </c>
-      <c r="I156" s="28" t="inlineStr">
-        <is>
-          <t>これからは死んだら
-デスペナルティが発生するから気をつけていってね。</t>
-        </is>
-      </c>
-      <c r="J156" s="19" t="inlineStr">
-        <is>
-          <t>From now on, when you die, you'll incur death penalties.
-So be careful.</t>
+        <v>232</v>
+      </c>
+      <c r="I156" s="26" t="inlineStr">
+        <is>
+          <t>さすがの私も、キミみたいな冒険者は初めてよ…</t>
+        </is>
+      </c>
+      <c r="J156" s="25" t="inlineStr">
+        <is>
+          <t>Even for me, I’ve never seen an adventurer quite like you...</t>
         </is>
       </c>
       <c r="K156" s="19" t="inlineStr">
         <is>
-          <t>De agora em diante, quando você morrer, incorrerá em uma penalidade de morte.
-Portanto, tenha cuidado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Até eu nunca vi um aventureiro como você...</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A157" s="19" t="n"/>
       <c r="B157" s="19" t="n"/>
       <c r="C157" s="19" t="n"/>
@@ -4703,17 +4731,31 @@
       <c r="E157" s="19" t="n"/>
       <c r="F157" s="19" t="n"/>
       <c r="G157" s="19" t="n"/>
-      <c r="I157" s="19" t="n"/>
-      <c r="J157" s="19" t="n"/>
-      <c r="K157" s="19" t="n"/>
+      <c r="H157" s="15" t="n">
+        <v>128</v>
+      </c>
+      <c r="I157" s="28" t="inlineStr">
+        <is>
+          <t>これからは死んだら
+デスペナルティが発生するから気をつけていってね。</t>
+        </is>
+      </c>
+      <c r="J157" s="19" t="inlineStr">
+        <is>
+          <t>From now on, when you die, you'll incur death penalties.
+So be careful.</t>
+        </is>
+      </c>
+      <c r="K157" s="19" t="inlineStr">
+        <is>
+          <t>De agora em diante, quando você morrer, sofrerá penalidades de morte.
+Então cuidado.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A158" s="19" t="n"/>
-      <c r="B158" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B158" s="19" t="n"/>
       <c r="C158" s="19" t="n"/>
       <c r="D158" s="19" t="n"/>
       <c r="E158" s="19" t="n"/>
@@ -4725,7 +4767,11 @@
     </row>
     <row r="159" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A159" s="19" t="n"/>
-      <c r="B159" s="19" t="n"/>
+      <c r="B159" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C159" s="19" t="n"/>
       <c r="D159" s="19" t="n"/>
       <c r="E159" s="19" t="n"/>
@@ -4736,11 +4782,7 @@
       <c r="K159" s="19" t="n"/>
     </row>
     <row r="160" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A160" s="19" t="inlineStr">
-        <is>
-          <t>garbage</t>
-        </is>
-      </c>
+      <c r="A160" s="19" t="n"/>
       <c r="B160" s="19" t="n"/>
       <c r="C160" s="19" t="n"/>
       <c r="D160" s="19" t="n"/>
@@ -4751,34 +4793,23 @@
       <c r="J160" s="19" t="n"/>
       <c r="K160" s="19" t="n"/>
     </row>
-    <row r="161" ht="13.8" customFormat="1" customHeight="1" s="15">
-      <c r="A161" s="19" t="n"/>
+    <row r="161" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A161" s="19" t="inlineStr">
+        <is>
+          <t>garbage</t>
+        </is>
+      </c>
       <c r="B161" s="19" t="n"/>
       <c r="C161" s="19" t="n"/>
       <c r="D161" s="19" t="n"/>
       <c r="E161" s="19" t="n"/>
       <c r="F161" s="19" t="n"/>
       <c r="G161" s="19" t="n"/>
-      <c r="H161" s="15" t="n">
-        <v>129</v>
-      </c>
-      <c r="I161" s="26" t="inlineStr">
-        <is>
-          <t>やだ、ゴミまみれ！</t>
-        </is>
-      </c>
-      <c r="J161" s="25" t="inlineStr">
-        <is>
-          <t>Oh no, there's trash everywhere!</t>
-        </is>
-      </c>
-      <c r="K161" s="19" t="inlineStr">
-        <is>
-          <t>Ah não, tem lixo por toda parte!</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="I161" s="19" t="n"/>
+      <c r="J161" s="19" t="n"/>
+      <c r="K161" s="19" t="n"/>
+    </row>
+    <row r="162" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A162" s="19" t="n"/>
       <c r="B162" s="19" t="n"/>
       <c r="C162" s="19" t="n"/>
@@ -4787,24 +4818,21 @@
       <c r="F162" s="19" t="n"/>
       <c r="G162" s="19" t="n"/>
       <c r="H162" s="15" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I162" s="26" t="inlineStr">
         <is>
-          <t>キミって、噂の…片づけられない冒険者なの？
-ゴミはちゃんと掃除しないと大問題になるわよ？</t>
-        </is>
-      </c>
-      <c r="J162" s="19" t="inlineStr">
-        <is>
-          <t>Are you the rumored... messy adventurer?
-If you don't clean up, it could become a big problem!</t>
+          <t>やだ、ゴミまみれ！</t>
+        </is>
+      </c>
+      <c r="J162" s="25" t="inlineStr">
+        <is>
+          <t>Oh no, there's trash everywhere!</t>
         </is>
       </c>
       <c r="K162" s="19" t="inlineStr">
         <is>
-          <t>Você é um daqueles aventureiros... Bagunceiros?
-Sabe, se você não limpar seu lixo, vai se meter em grandes problemas.</t>
+          <t>Ai não, lixo para todo lado!</t>
         </is>
       </c>
     </row>
@@ -4817,23 +4845,24 @@
       <c r="F163" s="19" t="n"/>
       <c r="G163" s="19" t="n"/>
       <c r="H163" s="15" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I163" s="26" t="inlineStr">
         <is>
-          <t>といっても、住民が増えてくるとゴミも多くなるから
-何らかの対策が必要ね！</t>
+          <t>キミって、噂の…片づけられない冒険者なの？
+ゴミはちゃんと掃除しないと大問題になるわよ？</t>
         </is>
       </c>
       <c r="J163" s="19" t="inlineStr">
         <is>
-          <t>As the population grows, more trash will accumulate,
-so you'll need to come up with some measures.</t>
+          <t>Are you the rumored... messy adventurer?
+If you don't clean up, it could become a big problem!</t>
         </is>
       </c>
       <c r="K163" s="19" t="inlineStr">
         <is>
-          <t>À medida que a população crescer, mais lixo se acumulará, portanto, você precisará tomar algumas medidas.</t>
+          <t>Você é o famoso... aventureiro bagunceiro?
+Se não limpar isso, pode virar um grande problema!</t>
         </is>
       </c>
     </row>
@@ -4846,28 +4875,28 @@
       <c r="F164" s="19" t="n"/>
       <c r="G164" s="19" t="n"/>
       <c r="H164" s="15" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I164" s="26" t="inlineStr">
         <is>
-          <t>一番手っ取り早い解決方法は
-「ポイ捨て厳罰法」を施行することかな。</t>
+          <t>といっても、住民が増えてくるとゴミも多くなるから
+何らかの対策が必要ね！</t>
         </is>
       </c>
       <c r="J164" s="19" t="inlineStr">
         <is>
-          <t>The quickest solution is to
-implement the "Strict Anti-Littering Law".</t>
+          <t>As the population grows, more trash will accumulate,
+so you'll need to come up with some measures.</t>
         </is>
       </c>
       <c r="K164" s="19" t="inlineStr">
         <is>
-          <t>A solução mais rápida é implementar a
-"Lei Rigorosa Contra o Descarte de Lixo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>Conforme a população cresce, mais lixo se acumula,
+então você vai precisar tomar alguma providência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A165" s="19" t="n"/>
       <c r="B165" s="19" t="n"/>
       <c r="C165" s="19" t="n"/>
@@ -4876,27 +4905,24 @@
       <c r="F165" s="19" t="n"/>
       <c r="G165" s="19" t="n"/>
       <c r="H165" s="15" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I165" s="26" t="inlineStr">
         <is>
-          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
-ただし、民度が下がってしまうので、いつかはもっと
-良いゴミ対策方法に移行したい所ね。</t>
+          <t>一番手っ取り早い解決方法は
+「ポイ捨て厳罰法」を施行することかな。</t>
         </is>
       </c>
       <c r="J165" s="19" t="inlineStr">
         <is>
-          <t>With this policy, trash will mostly disappear.
-However, since it lowers the public morality,
-you'll eventually want to switch to a better waste management solution.</t>
+          <t>The quickest solution is to
+implement the "Strict Anti-Littering Law".</t>
         </is>
       </c>
       <c r="K165" s="19" t="inlineStr">
         <is>
-          <t>Com essa política, o lixo praticamente desaparecerá._x000D_
-No entanto, como isso reduz a moral pública,_x000D_
-eventualmente você vai querer mudar para uma solução melhor de gestão de resíduos.</t>
+          <t>A solução mais rápida é
+ativar a "Lei Antimato Estrita".</t>
         </is>
       </c>
     </row>
@@ -4909,29 +4935,31 @@
       <c r="F166" s="19" t="n"/>
       <c r="G166" s="19" t="n"/>
       <c r="H166" s="15" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I166" s="26" t="inlineStr">
         <is>
-          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
-住人は民度の高さに応じて
-自動的にゴミを出してくれるわ。</t>
+          <t>このポリシーを施行すると、ゴミはほとんど発生しなくなるわ。
+ただし、民度が下がってしまうので、いつかはもっと
+良いゴミ対策方法に移行したい所ね。</t>
         </is>
       </c>
       <c r="J166" s="19" t="inlineStr">
         <is>
-          <t>Putting up garbage dump signs and placing garbage containers
-will encourage residents to dispose of trash according to the public morality.</t>
+          <t>With this policy, trash will mostly disappear.
+However, since it lowers the public morality,
+you'll eventually want to switch to a better waste management solution.</t>
         </is>
       </c>
       <c r="K166" s="19" t="inlineStr">
         <is>
-          <t>Colocar placas de descarte e posicionar lixeiras
-incentivará os moradores a jogarem o lixo no lugar certo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t>Com esta política, o lixo quase desaparece.
+Porém, como ela abaixa a moral pública,
+cedo ou tarde você vai querer trocar por uma solução de saneamento melhor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A167" s="19" t="n"/>
       <c r="B167" s="19" t="n"/>
       <c r="C167" s="19" t="n"/>
@@ -4940,23 +4968,25 @@
       <c r="F167" s="19" t="n"/>
       <c r="G167" s="19" t="n"/>
       <c r="H167" s="15" t="n">
-        <v>135</v>
-      </c>
-      <c r="I167" s="28" t="inlineStr">
-        <is>
-          <t>それに、掃除をしてくれる住民がいれば
-ゴミを分別して出す確率も大幅に上昇するの。</t>
+        <v>134</v>
+      </c>
+      <c r="I167" s="26" t="inlineStr">
+        <is>
+          <t>ゴミ捨て場の立札を立てたり、ゴミのコンテナを置けば
+住人は民度の高さに応じて
+自動的にゴミを出してくれるわ。</t>
         </is>
       </c>
       <c r="J167" s="19" t="inlineStr">
         <is>
-          <t>And if you have residents who clean up,
-the chances of them sorting the trash increase significantly.</t>
+          <t>Putting up garbage dump signs and placing garbage containers
+will encourage residents to dispose of trash according to the public morality.</t>
         </is>
       </c>
       <c r="K167" s="19" t="inlineStr">
         <is>
-          <t>Além disso, a probabilidade de separar e descartar o lixo aumenta consideravelmente quando há moradores dispostos a fazer a limpeza.</t>
+          <t>Colocar placas de lixão e contêineres de lixo
+incentiva os moradores a descartarem conforme a moral pública.</t>
         </is>
       </c>
     </row>
@@ -4969,46 +4999,64 @@
       <c r="F168" s="19" t="n"/>
       <c r="G168" s="19" t="n"/>
       <c r="H168" s="15" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I168" s="28" t="inlineStr">
         <is>
-          <t>ゴミは解体することで貴重な資源になるから
-有効に活用していきたいところね！</t>
+          <t>それに、掃除をしてくれる住民がいれば
+ゴミを分別して出す確率も大幅に上昇するの。</t>
         </is>
       </c>
       <c r="J168" s="19" t="inlineStr">
         <is>
-          <t>Garbages can be dismantled into valuable resources,
-so you'll want to use them effectively!</t>
+          <t>And if you have residents who clean up,
+the chances of them sorting the trash increase significantly.</t>
         </is>
       </c>
       <c r="K168" s="19" t="inlineStr">
         <is>
-          <t>Os lixos podem ser desmontados em recursos valiosos,_x000D_
-então use-os de forma eficiente!</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>E se você tiver moradores que limpam,
+a chance de eles separarem o lixo aumenta bastante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A169" s="19" t="n"/>
-      <c r="B169" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B169" s="19" t="n"/>
       <c r="C169" s="19" t="n"/>
       <c r="D169" s="19" t="n"/>
       <c r="E169" s="19" t="n"/>
       <c r="F169" s="19" t="n"/>
       <c r="G169" s="19" t="n"/>
-      <c r="I169" s="19" t="n"/>
-      <c r="J169" s="19" t="n"/>
-      <c r="K169" s="19" t="n"/>
+      <c r="H169" s="15" t="n">
+        <v>136</v>
+      </c>
+      <c r="I169" s="28" t="inlineStr">
+        <is>
+          <t>ゴミは解体することで貴重な資源になるから
+有効に活用していきたいところね！</t>
+        </is>
+      </c>
+      <c r="J169" s="19" t="inlineStr">
+        <is>
+          <t>Garbages can be dismantled into valuable resources,
+so you'll want to use them effectively!</t>
+        </is>
+      </c>
+      <c r="K169" s="19" t="inlineStr">
+        <is>
+          <t>Lixos podem ser desmontados em recursos valiosos,
+então vale usá-los bem!</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A170" s="19" t="n"/>
-      <c r="B170" s="19" t="n"/>
+      <c r="B170" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C170" s="19" t="n"/>
       <c r="D170" s="19" t="n"/>
       <c r="E170" s="19" t="n"/>
@@ -5019,11 +5067,7 @@
       <c r="K170" s="19" t="n"/>
     </row>
     <row r="171" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A171" s="19" t="inlineStr">
-        <is>
-          <t>eq</t>
-        </is>
-      </c>
+      <c r="A171" s="19" t="n"/>
       <c r="B171" s="19" t="n"/>
       <c r="C171" s="19" t="n"/>
       <c r="D171" s="19" t="n"/>
@@ -5034,37 +5078,23 @@
       <c r="J171" s="19" t="n"/>
       <c r="K171" s="19" t="n"/>
     </row>
-    <row r="172" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="A172" s="19" t="n"/>
+    <row r="172" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A172" s="19" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
       <c r="B172" s="19" t="n"/>
       <c r="C172" s="19" t="n"/>
       <c r="D172" s="19" t="n"/>
       <c r="E172" s="19" t="n"/>
       <c r="F172" s="19" t="n"/>
       <c r="G172" s="19" t="n"/>
-      <c r="H172" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="I172" s="26" t="inlineStr">
-        <is>
-          <t>ん、洞窟の探索？
-キミも冒険者らしくなってきたわね！</t>
-        </is>
-      </c>
-      <c r="J172" s="25" t="inlineStr">
-        <is>
-          <t>Huh, exploring a cave already?
-You're becoming like a real adventurer!</t>
-        </is>
-      </c>
-      <c r="K172" s="19" t="inlineStr">
-        <is>
-          <t>Já está explorando uma caverna?
-Você está se tornando um verdadeiro aventureiro!</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="13.8" customFormat="1" customHeight="1" s="15">
+      <c r="I172" s="19" t="n"/>
+      <c r="J172" s="19" t="n"/>
+      <c r="K172" s="19" t="n"/>
+    </row>
+    <row r="173" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A173" s="19" t="n"/>
       <c r="B173" s="19" t="n"/>
       <c r="C173" s="19" t="n"/>
@@ -5073,21 +5103,24 @@
       <c r="F173" s="19" t="n"/>
       <c r="G173" s="19" t="n"/>
       <c r="H173" s="15" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I173" s="26" t="inlineStr">
         <is>
-          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
+          <t>ん、洞窟の探索？
+キミも冒険者らしくなってきたわね！</t>
         </is>
       </c>
       <c r="J173" s="25" t="inlineStr">
         <is>
-          <t>But before you go deeper, take a look at yourself.</t>
+          <t>Huh, exploring a cave already?
+You're becoming like a real adventurer!</t>
         </is>
       </c>
       <c r="K173" s="19" t="inlineStr">
         <is>
-          <t>Mas antes de ir mais fundo, dê uma olhada em si mesmo.</t>
+          <t>Hã, explorando uma caverna já?
+Você está virando um aventureiro de verdade!</t>
         </is>
       </c>
     </row>
@@ -5100,25 +5133,25 @@
       <c r="F174" s="19" t="n"/>
       <c r="G174" s="19" t="n"/>
       <c r="H174" s="15" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I174" s="26" t="inlineStr">
         <is>
-          <t>…そんな装備で大丈夫か？</t>
+          <t>でも、奥に進む前にちょっと自分の姿を確認してみて。</t>
         </is>
       </c>
       <c r="J174" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">...You sure that's enough armor? </t>
+          <t>But before you go deeper, take a look at yourself.</t>
         </is>
       </c>
       <c r="K174" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">... Tem certeza de que essa armadura é suficiente? </t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>Mas antes de descer mais, dê uma olhada em você mesmo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A175" s="19" t="n"/>
       <c r="B175" s="19" t="n"/>
       <c r="C175" s="19" t="n"/>
@@ -5127,31 +5160,25 @@
       <c r="F175" s="19" t="n"/>
       <c r="G175" s="19" t="n"/>
       <c r="H175" s="15" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I175" s="26" t="inlineStr">
         <is>
-          <t>洞窟ともなると、敵もたくさん出てくるわ。
-もし装備を身につけていない部位が３つも４つもあるなら
-たぶん出直した方がキミの命のためよ。</t>
+          <t>…そんな装備で大丈夫か？</t>
         </is>
       </c>
       <c r="J175" s="25" t="inlineStr">
         <is>
-          <t>Caves have lots of enemies.
-If you have an unequipped slot or two,
-you might want to turn back for your own safety.</t>
+          <t xml:space="preserve">...You sure that's enough armor? </t>
         </is>
       </c>
       <c r="K175" s="19" t="inlineStr">
         <is>
-          <t>As cavernas estão cheias de inimigos._x000D_
-Se você tiver um ou dois espaços de equipamento vazios,_x000D_
-talvez seja melhor voltar para sua própria segurança.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="23.85" customFormat="1" customHeight="1" s="15">
+          <t xml:space="preserve">...Tem certeza de que é armadura suficiente? </t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A176" s="19" t="n"/>
       <c r="B176" s="19" t="n"/>
       <c r="C176" s="19" t="n"/>
@@ -5160,28 +5187,31 @@
       <c r="F176" s="19" t="n"/>
       <c r="G176" s="19" t="n"/>
       <c r="H176" s="15" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I176" s="26" t="inlineStr">
         <is>
-          <t>拠点では、簡単な武器や防具を製作することもできるし
-街に赴いて店で物色してもいい。</t>
+          <t>洞窟ともなると、敵もたくさん出てくるわ。
+もし装備を身につけていない部位が３つも４つもあるなら
+たぶん出直した方がキミの命のためよ。</t>
         </is>
       </c>
       <c r="J176" s="25" t="inlineStr">
         <is>
-          <t>At your base, you can craft simple weapons and armor,
-or you can browse the shops in town.</t>
+          <t>Caves have lots of enemies.
+If you have an unequipped slot or two,
+you might want to turn back for your own safety.</t>
         </is>
       </c>
       <c r="K176" s="19" t="inlineStr">
         <is>
-          <t>Na sua base, você pode fabricar armas e armaduras simples,_x000D_
-ou dar uma olhada nas lojas da cidade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="35.05" customFormat="1" customHeight="1" s="15">
+          <t>Cavernas têm muitos inimigos.
+Se você tem um slot ou outro sem equipar,
+talvez queira voltar por segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="23.85" customFormat="1" customHeight="1" s="15">
       <c r="A177" s="19" t="n"/>
       <c r="B177" s="19" t="n"/>
       <c r="C177" s="19" t="n"/>
@@ -5190,53 +5220,67 @@
       <c r="F177" s="19" t="n"/>
       <c r="G177" s="19" t="n"/>
       <c r="H177" s="15" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I177" s="26" t="inlineStr">
         <is>
-          <t>特に防御力(PV）は、敵からのダメージを軽減する
-重要なステータスだから、敵からの攻撃が辛いと感じたら
-防御力をあげてみてね。</t>
+          <t>拠点では、簡単な武器や防具を製作することもできるし
+街に赴いて店で物色してもいい。</t>
         </is>
       </c>
       <c r="J177" s="25" t="inlineStr">
         <is>
-          <t>Protection Value (PV) is especially a crucial stat that
-reduces the damage you take from enemies.
-If you find enemy attacks too harsh, try increasing your defense.</t>
+          <t>At your base, you can craft simple weapons and armor,
+or you can browse the shops in town.</t>
         </is>
       </c>
       <c r="K177" s="19" t="inlineStr">
         <is>
-          <t>O Valor de Proteção (VP ou PV) é um atributo crucial que
-reduz o dano recebido dos inimigos.
-Se os ataques dos inimigos estiverem muito fortes, tente aumentar sua defesa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Na sua base, você pode fabricar armas e armaduras simples,
+ou garimpar as lojas da cidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A178" s="19" t="n"/>
-      <c r="B178" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B178" s="19" t="n"/>
       <c r="C178" s="19" t="n"/>
       <c r="D178" s="19" t="n"/>
       <c r="E178" s="19" t="n"/>
       <c r="F178" s="19" t="n"/>
       <c r="G178" s="19" t="n"/>
-      <c r="I178" s="19" t="n"/>
-      <c r="J178" s="19" t="n"/>
-      <c r="K178" s="19" t="n"/>
+      <c r="H178" s="15" t="n">
+        <v>142</v>
+      </c>
+      <c r="I178" s="26" t="inlineStr">
+        <is>
+          <t>特に防御力(PV）は、敵からのダメージを軽減する
+重要なステータスだから、敵からの攻撃が辛いと感じたら
+防御力をあげてみてね。</t>
+        </is>
+      </c>
+      <c r="J178" s="25" t="inlineStr">
+        <is>
+          <t>Protection Value (PV) is especially a crucial stat that
+reduces the damage you take from enemies.
+If you find enemy attacks too harsh, try increasing your defense.</t>
+        </is>
+      </c>
+      <c r="K178" s="19" t="inlineStr">
+        <is>
+          <t>O Valor de Proteção (PV) é um status crucial que
+reduz o dano que você sofre dos inimigos.
+Se os ataques inimigos estiverem pesados demais, tente aumentar a defesa.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A179" s="19" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
-      <c r="B179" s="19" t="n"/>
+      <c r="A179" s="19" t="n"/>
+      <c r="B179" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C179" s="19" t="n"/>
       <c r="D179" s="19" t="n"/>
       <c r="E179" s="19" t="n"/>
@@ -5246,34 +5290,23 @@
       <c r="J179" s="19" t="n"/>
       <c r="K179" s="19" t="n"/>
     </row>
-    <row r="180" ht="13.8" customFormat="1" customHeight="1" s="15">
-      <c r="A180" s="19" t="n"/>
+    <row r="180" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A180" s="19" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
       <c r="B180" s="19" t="n"/>
       <c r="C180" s="19" t="n"/>
       <c r="D180" s="19" t="n"/>
       <c r="E180" s="19" t="n"/>
       <c r="F180" s="19" t="n"/>
       <c r="G180" s="19" t="n"/>
-      <c r="H180" s="15" t="n">
-        <v>143</v>
-      </c>
-      <c r="I180" s="26" t="inlineStr">
-        <is>
-          <t>よしよし、盟約の石も育ってきたわ。</t>
-        </is>
-      </c>
-      <c r="J180" s="25" t="inlineStr">
-        <is>
-          <t>Well done, your Hearth Stone is growing.</t>
-        </is>
-      </c>
-      <c r="K180" s="19" t="inlineStr">
-        <is>
-          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="I180" s="19" t="n"/>
+      <c r="J180" s="19" t="n"/>
+      <c r="K180" s="19" t="n"/>
+    </row>
+    <row r="181" ht="13.8" customFormat="1" customHeight="1" s="15">
       <c r="A181" s="19" t="n"/>
       <c r="B181" s="19" t="n"/>
       <c r="C181" s="19" t="n"/>
@@ -5282,27 +5315,21 @@
       <c r="F181" s="19" t="n"/>
       <c r="G181" s="19" t="n"/>
       <c r="H181" s="15" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I181" s="26" t="inlineStr">
         <is>
-          <t>そう、この謎の石は、なんと成長するのよ。
-石の成長とともに、キミの拠点は様々な恩恵を受けるの。
-住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
-        </is>
-      </c>
-      <c r="J181" s="19" t="inlineStr">
-        <is>
-          <t>Yes, this mysterious stone actually grows.
-And as it grows, your base receives various benefits,
-like an increased maximum number of residents or new policies.</t>
+          <t>よしよし、盟約の石も育ってきたわ。</t>
+        </is>
+      </c>
+      <c r="J181" s="25" t="inlineStr">
+        <is>
+          <t>Well done, your Hearth Stone is growing.</t>
         </is>
       </c>
       <c r="K181" s="19" t="inlineStr">
         <is>
-          <t>Sim, essa pedra misteriosa realmente cresce.
-E conforme cresce, sua base recebe vários benefícios,
-como um aumento no número máximo de residentes ou novas políticas.</t>
+          <t>Muito bem, sua Pedra do Lar está crescendo.</t>
         </is>
       </c>
     </row>
@@ -5315,25 +5342,27 @@
       <c r="F182" s="19" t="n"/>
       <c r="G182" s="19" t="n"/>
       <c r="H182" s="15" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I182" s="26" t="inlineStr">
         <is>
-          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
-石のレベルがあがれば、その破壊だって防いでくれるのよ？
-まあ…拠点の中だけだけどね。</t>
+          <t>そう、この謎の石は、なんと成長するのよ。
+石の成長とともに、キミの拠点は様々な恩恵を受けるの。
+住民の最大数があがったり、新しいポリシーを覚えたりね。</t>
         </is>
       </c>
       <c r="J182" s="19" t="inlineStr">
         <is>
-          <t>Some enemies can use elemental attacks to destroy your items and equipment,
-but if the stone levels up, it can even prevent that within your base.</t>
+          <t>Yes, this mysterious stone actually grows.
+And as it grows, your base receives various benefits,
+like an increased maximum number of residents or new policies.</t>
         </is>
       </c>
       <c r="K182" s="19" t="inlineStr">
         <is>
-          <t>Alguns inimigos podem usar ataques elementais para destruir seus itens e equipamentos,
-mas se a pedra subir de nível, ela pode até impedir isso dentro da sua base.</t>
+          <t>Sim, esta pedra misteriosa realmente cresce.
+E conforme cresce, sua base recebe vários benefícios,
+como mais moradores no máximo ou políticas novas.</t>
         </is>
       </c>
     </row>
@@ -5346,31 +5375,29 @@
       <c r="F183" s="19" t="n"/>
       <c r="G183" s="19" t="n"/>
       <c r="H183" s="15" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I183" s="26" t="inlineStr">
         <is>
-          <t>出荷や日数の経過で、石は自動的に育っていくわ。
-…ただ、注意したいのは、石のレベルがあがると
-拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
+          <t>敵の中には、属性攻撃でアイテムや装備を破壊してくる厄介なのもいるけど
+石のレベルがあがれば、その破壊だって防いでくれるのよ？
+まあ…拠点の中だけだけどね。</t>
         </is>
       </c>
       <c r="J183" s="19" t="inlineStr">
         <is>
-          <t>The stone grows automatically through shipments and the passage of days.
-...But beware, as the stone levels up, the danger level of your base
-also increases... meaning stronger enemies will appear.</t>
+          <t>Some enemies can use elemental attacks to destroy your items and equipment,
+but if the stone levels up, it can even prevent that within your base.</t>
         </is>
       </c>
       <c r="K183" s="19" t="inlineStr">
         <is>
-          <t>A pedra cresce automaticamente com remessas e com a passagem dos dias.
-... Mas cuidado, à medida que a pedra sobe de nível, o nível de perigo da sua base
-também aumenta... Ou seja, inimigos mais fortes aparecerão.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="46.25" customFormat="1" customHeight="1" s="15">
+          <t>Alguns inimigos usam ataques elementais para destruir seus itens e equipamentos,
+mas se a pedra subir de nível, ela pode até impedir isso dentro da base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="35.05" customFormat="1" customHeight="1" s="15">
       <c r="A184" s="19" t="n"/>
       <c r="B184" s="19" t="n"/>
       <c r="C184" s="19" t="n"/>
@@ -5379,32 +5406,31 @@
       <c r="F184" s="19" t="n"/>
       <c r="G184" s="19" t="n"/>
       <c r="H184" s="15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I184" s="26" t="inlineStr">
         <is>
-          <t>「成長抑止」のポリシーを施行すれば、石の成長に
-ストップをかけることができる。
-もし今拠点に現れる敵に手こずるようだったら
-このポリシーを使って成長を止めておいた方がいいわね。</t>
+          <t>出荷や日数の経過で、石は自動的に育っていくわ。
+…ただ、注意したいのは、石のレベルがあがると
+拠点の危険度もあがる…つまり、強い敵が襲ってくるということね。</t>
         </is>
       </c>
       <c r="J184" s="19" t="inlineStr">
         <is>
-          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
-If you're struggling with the enemies currently appearing at your base,
-it might be a good idea to use this policy to halt the growth for a while.</t>
+          <t>The stone grows automatically through shipments and the passage of days.
+...But beware, as the stone levels up, the danger level of your base
+also increases... meaning stronger enemies will appear.</t>
         </is>
       </c>
       <c r="K184" s="19" t="inlineStr">
         <is>
-          <t>Você pode usar a política "Supressão de Crescimento" para impedir o crescimento da pedra.
-Se estiver tendo dificuldades com os inimigos que estão aparecendo na sua base,
-talvez seja uma boa ideia usar essa política para interromper o crescimento por um tempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>A pedra cresce sozinha com despachos e com a passagem dos dias.
+...Mas atenção: conforme a pedra sobe de nível, o nível de perigo da sua base
+também sobe... ou seja, inimigos mais fortes aparecem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="46.25" customFormat="1" customHeight="1" s="15">
       <c r="A185" s="19" t="n"/>
       <c r="B185" s="19" t="n"/>
       <c r="C185" s="19" t="n"/>
@@ -5412,9 +5438,31 @@
       <c r="E185" s="19" t="n"/>
       <c r="F185" s="19" t="n"/>
       <c r="G185" s="19" t="n"/>
-      <c r="I185" s="19" t="n"/>
-      <c r="J185" s="19" t="n"/>
-      <c r="K185" s="19" t="n"/>
+      <c r="H185" s="15" t="n">
+        <v>147</v>
+      </c>
+      <c r="I185" s="26" t="inlineStr">
+        <is>
+          <t>「成長抑止」のポリシーを施行すれば、石の成長に
+ストップをかけることができる。
+もし今拠点に現れる敵に手こずるようだったら
+このポリシーを使って成長を止めておいた方がいいわね。</t>
+        </is>
+      </c>
+      <c r="J185" s="19" t="inlineStr">
+        <is>
+          <t>You can use the "Growth Suppression" policy to stop the stone's growth.
+If you're struggling with the enemies currently appearing at your base,
+it might be a good idea to use this policy to halt the growth for a while.</t>
+        </is>
+      </c>
+      <c r="K185" s="19" t="inlineStr">
+        <is>
+          <t>Você pode usar a política "Supressão de Crescimento" para frear o crescimento da pedra.
+Se você está apanhando dos inimigos que surgem na base,
+pode ser bom usar esta política para pausar o crescimento por um tempo.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A186" s="19" t="n"/>
@@ -5430,11 +5478,7 @@
     </row>
     <row r="187" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A187" s="19" t="n"/>
-      <c r="B187" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B187" s="19" t="n"/>
       <c r="C187" s="19" t="n"/>
       <c r="D187" s="19" t="n"/>
       <c r="E187" s="19" t="n"/>
@@ -5445,12 +5489,12 @@
       <c r="K187" s="19" t="n"/>
     </row>
     <row r="188" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A188" s="19" t="inlineStr">
-        <is>
-          <t>feat</t>
-        </is>
-      </c>
-      <c r="B188" s="19" t="n"/>
+      <c r="A188" s="19" t="n"/>
+      <c r="B188" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
       <c r="C188" s="19" t="n"/>
       <c r="D188" s="19" t="n"/>
       <c r="E188" s="19" t="n"/>
@@ -5461,31 +5505,20 @@
       <c r="K188" s="19" t="n"/>
     </row>
     <row r="189" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A189" s="19" t="n"/>
+      <c r="A189" s="19" t="inlineStr">
+        <is>
+          <t>feat</t>
+        </is>
+      </c>
       <c r="B189" s="19" t="n"/>
       <c r="C189" s="19" t="n"/>
       <c r="D189" s="19" t="n"/>
       <c r="E189" s="19" t="n"/>
       <c r="F189" s="19" t="n"/>
       <c r="G189" s="19" t="n"/>
-      <c r="H189" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="I189" s="19" t="inlineStr">
-        <is>
-          <t>フィートポイントの獲得おめでとう！</t>
-        </is>
-      </c>
-      <c r="J189" s="25" t="inlineStr">
-        <is>
-          <t>Congratulations on earning a Feat Point!</t>
-        </is>
-      </c>
-      <c r="K189" s="19" t="inlineStr">
-        <is>
-          <t>Parabéns por ganhar um Ponto de Talento!</t>
-        </is>
-      </c>
+      <c r="I189" s="19" t="n"/>
+      <c r="J189" s="19" t="n"/>
+      <c r="K189" s="19" t="n"/>
     </row>
     <row r="190" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A190" s="19" t="n"/>
@@ -5496,25 +5529,25 @@
       <c r="F190" s="19" t="n"/>
       <c r="G190" s="19" t="n"/>
       <c r="H190" s="15" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I190" s="19" t="inlineStr">
         <is>
-          <t>…え？　フィート、知らないの？</t>
-        </is>
-      </c>
-      <c r="J190" s="19" t="inlineStr">
-        <is>
-          <t>...Huh? You don’t know about Feats?</t>
+          <t>フィートポイントの獲得おめでとう！</t>
+        </is>
+      </c>
+      <c r="J190" s="25" t="inlineStr">
+        <is>
+          <t>Congratulations on earning a Feat Point!</t>
         </is>
       </c>
       <c r="K190" s="19" t="inlineStr">
         <is>
-          <t>Você não conhece os talentos?</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Parabéns por ganhar um Ponto de Dote!</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="A191" s="19" t="n"/>
       <c r="B191" s="19" t="n"/>
       <c r="C191" s="19" t="n"/>
@@ -5523,26 +5556,21 @@
       <c r="F191" s="19" t="n"/>
       <c r="G191" s="19" t="n"/>
       <c r="H191" s="15" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I191" s="19" t="inlineStr">
         <is>
-          <t>足が速かったり、力が強かったり
-そういうキミの特徴をフィートっていって
-フィートポイントを消費することで獲得できるの。</t>
+          <t>…え？　フィート、知らないの？</t>
         </is>
       </c>
       <c r="J191" s="19" t="inlineStr">
         <is>
-          <t>Feats are special traits you have,
-like being really fast or super strong.
-You can earn them by using Feat Points.</t>
+          <t>...Huh? You don’t know about Feats?</t>
         </is>
       </c>
       <c r="K191" s="19" t="inlineStr">
         <is>
-          <t>Talentos são características especiais que você tem, como ser muito rápido ou superforte.
-Você pode certas características usando Pontos de Talentos.</t>
+          <t>...Hã? Você não sabe o que são Dotes?</t>
         </is>
       </c>
     </row>
@@ -5555,31 +5583,31 @@
       <c r="F192" s="19" t="n"/>
       <c r="G192" s="19" t="n"/>
       <c r="H192" s="15" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I192" s="19" t="inlineStr">
         <is>
-          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
-キミが何か行動して成長すると、このゲージは増えていく。
-ゲージが満杯になると、フィートポイントを貰えるわ。</t>
+          <t>足が速かったり、力が強かったり
+そういうキミの特徴をフィートっていって
+フィートポイントを消費することで獲得できるの。</t>
         </is>
       </c>
       <c r="J192" s="19" t="inlineStr">
         <is>
-          <t>Do you see the blue feather icon at the bottom of your screen?
-When you perform actions and grow, this gauge fills up.
-Once it’s full, you earn a Feat Point.</t>
+          <t>Feats are special traits you have,
+like being really fast or super strong.
+You can earn them by using Feat Points.</t>
         </is>
       </c>
       <c r="K192" s="19" t="inlineStr">
         <is>
-          <t>Você vê o ícone de pena azul na parte inferior da tela?
-Quando você realiza ações e cresce, esse medidor se enche.
-Quando ele estiver cheio, você ganha um Ponto de Talento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="43.25" customFormat="1" customHeight="1" s="15">
+          <t>Dotes são traços especiais seus,
+como ser muito rápido ou super forte.
+Você os ganha usando Pontos de Dote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A193" s="19" t="n"/>
       <c r="B193" s="19" t="n"/>
       <c r="C193" s="19" t="n"/>
@@ -5588,30 +5616,31 @@
       <c r="F193" s="19" t="n"/>
       <c r="G193" s="19" t="n"/>
       <c r="H193" s="15" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I193" s="19" t="inlineStr">
         <is>
-          <t>ゲージをクリックすると、キミが獲得できる
-フィートの一覧が表示されるでしょ？
-この中から、キミが役に立ちそうと思うフィートを
-選択して見るといいわ。</t>
+          <t>画面の下に、青い羽マークのアイコンのゲージが見える？
+キミが何か行動して成長すると、このゲージは増えていく。
+ゲージが満杯になると、フィートポイントを貰えるわ。</t>
         </is>
       </c>
       <c r="J193" s="19" t="inlineStr">
         <is>
-          <t>Click on the gauge to see a list of Feats you can acquire.
-Choose the ones you think will be useful to you.</t>
+          <t>Do you see the blue feather icon at the bottom of your screen?
+When you perform actions and grow, this gauge fills up.
+Once it’s full, you earn a Feat Point.</t>
         </is>
       </c>
       <c r="K193" s="19" t="inlineStr">
         <is>
-          <t>Clique no medidor para ver uma lista de Talentos que você pode adquirir.
-Escolha os que achar que serão úteis para você.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="32.8" customFormat="1" customHeight="1" s="15">
+          <t>Vê o ícone de pena azul no rodapé da tela?
+Quando você age e cresce, este medidor enche.
+Quando enche, você ganha um Ponto de Dote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="43.25" customFormat="1" customHeight="1" s="15">
       <c r="A194" s="19" t="n"/>
       <c r="B194" s="19" t="n"/>
       <c r="C194" s="19" t="n"/>
@@ -5620,30 +5649,30 @@
       <c r="F194" s="19" t="n"/>
       <c r="G194" s="19" t="n"/>
       <c r="H194" s="15" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I194" s="19" t="inlineStr">
         <is>
-          <t>フィートポイントは、貯めておくこともできるから
-今自分に足りないと思うものが特になければ
-温存しておくのもいい選択ね。</t>
+          <t>ゲージをクリックすると、キミが獲得できる
+フィートの一覧が表示されるでしょ？
+この中から、キミが役に立ちそうと思うフィートを
+選択して見るといいわ。</t>
         </is>
       </c>
       <c r="J194" s="19" t="inlineStr">
         <is>
-          <t>You can also save your Feat Points
-if you don’t need anything specific right now.
-It’s a good strategy to save them for later.</t>
+          <t>Click on the gauge to see a list of Feats you can acquire.
+Choose the ones you think will be useful to you.</t>
         </is>
       </c>
       <c r="K194" s="19" t="inlineStr">
         <is>
-          <t>Você também pode salvar seus Pontos de Talentos se não precisar de nada específico no momento.
-É uma boa estratégia guardá-los para mais tarde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="32.8" customHeight="1" s="17">
+          <t>Clique no medidor para ver a lista de Dotes que pode adquirir.
+Escolha os que você achar úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="32.8" customFormat="1" customHeight="1" s="15">
       <c r="A195" s="19" t="n"/>
       <c r="B195" s="19" t="n"/>
       <c r="C195" s="19" t="n"/>
@@ -5652,257 +5681,292 @@
       <c r="F195" s="19" t="n"/>
       <c r="G195" s="19" t="n"/>
       <c r="H195" s="15" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I195" s="19" t="inlineStr">
         <is>
-          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
-例えば「美食家」のフィートは
-「料理」スキルを覚えていなければ表示されないの。</t>
+          <t>フィートポイントは、貯めておくこともできるから
+今自分に足りないと思うものが特になければ
+温存しておくのもいい選択ね。</t>
         </is>
       </c>
       <c r="J195" s="19" t="inlineStr">
         <is>
-          <t>Note that some Feats have prerequisites.
-For example, the “Gourmet” Feat won’t appear
-unless you’ve learned the “Cooking” skill.</t>
+          <t>You can also save your Feat Points
+if you don’t need anything specific right now.
+It’s a good strategy to save them for later.</t>
         </is>
       </c>
       <c r="K195" s="19" t="inlineStr">
         <is>
-          <t>Observe que alguns Talentos têm pré-requisitos.
-Por exemplo, o Talento “Gourmet” não aparecerá a menos que você tenha aprendido a habilidade “Culinária”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="12.8" customFormat="1" customHeight="1" s="15">
+          <t>Você também pode guardar seus Pontos de Dote
+se não precisar de nada específico agora.
+Guardar para depois é uma boa estratégia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="32.8" customHeight="1" s="17">
       <c r="A196" s="19" t="n"/>
-      <c r="B196" s="19" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
+      <c r="B196" s="19" t="n"/>
       <c r="C196" s="19" t="n"/>
       <c r="D196" s="19" t="n"/>
       <c r="E196" s="19" t="n"/>
       <c r="F196" s="19" t="n"/>
       <c r="G196" s="19" t="n"/>
-      <c r="I196" s="19" t="n"/>
-      <c r="J196" s="19" t="n"/>
-      <c r="K196" s="19" t="n"/>
+      <c r="H196" s="15" t="n">
+        <v>154</v>
+      </c>
+      <c r="I196" s="19" t="inlineStr">
+        <is>
+          <t>ちなみに、獲得に前提条件のあるフィートもあるからね。
+例えば「美食家」のフィートは
+「料理」スキルを覚えていなければ表示されないの。</t>
+        </is>
+      </c>
+      <c r="J196" s="19" t="inlineStr">
+        <is>
+          <t>Note that some Feats have prerequisites.
+For example, the “Gourmet” Feat won’t appear
+unless you’ve learned the “Cooking” skill.</t>
+        </is>
+      </c>
+      <c r="K196" s="19" t="inlineStr">
+        <is>
+          <t>Repare que alguns Dotes têm pré-requisitos.
+Por exemplo, o Dote "Gourmet" não aparece
+se você não aprendeu a perícia "Cozinha".</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B197" s="19" t="n"/>
+      <c r="A197" s="19" t="n"/>
+      <c r="B197" s="19" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="n"/>
+      <c r="D197" s="19" t="n"/>
+      <c r="E197" s="19" t="n"/>
+      <c r="F197" s="19" t="n"/>
+      <c r="G197" s="19" t="n"/>
+      <c r="I197" s="19" t="n"/>
+      <c r="J197" s="19" t="n"/>
+      <c r="K197" s="19" t="n"/>
     </row>
     <row r="198" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A198" s="19" t="inlineStr">
+      <c r="B198" s="19" t="n"/>
+    </row>
+    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A199" s="19" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H200" s="15" t="n">
+    <row r="200" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="201" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H201" s="15" t="n">
         <v>105</v>
       </c>
-      <c r="I200" s="19" t="inlineStr">
+      <c r="I201" s="19" t="inlineStr">
         <is>
           <t>よしよし、丸太さんを手に入れたのね。</t>
         </is>
       </c>
-      <c r="J200" s="25" t="inlineStr">
+      <c r="J201" s="25" t="inlineStr">
         <is>
           <t>Alright, you got a log!</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Muito bem, você conseguiu um tronco!</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H201" s="15" t="n">
+      <c r="K201" s="15" t="inlineStr">
+        <is>
+          <t>Isso, você conseguiu um tronco!</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H202" s="15" t="n">
         <v>106</v>
       </c>
-      <c r="I201" s="19" t="inlineStr">
+      <c r="I202" s="19" t="inlineStr">
         <is>
           <t>丸太さん、いえ、丸太先生は最も基本的なクラフト素材で
 焚火などの燃料としても使える優れモノよ。</t>
         </is>
       </c>
-      <c r="J201" s="19" t="inlineStr">
+      <c r="J202" s="19" t="inlineStr">
         <is>
           <t>Logs, or should I say, Mr. Log, are the most basic crafting materials.
 They’re also excellent for things like campfire fuel.</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Os Troncos, ou melhor, o Sr. Tronco, são os materiais de fabricação mais básicos.
-Elas também são excelentes para coisas como combustível para fogueira.</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H202" s="15" t="n">
+      <c r="K202" s="15" t="inlineStr">
+        <is>
+          <t>Troncos, ou melhor, Sr. Tronco, são o material de fabricação mais básico.
+Também são excelentes como lenha de fogueira, por exemplo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H203" s="15" t="n">
         <v>107</v>
       </c>
-      <c r="I202" s="19" t="inlineStr">
+      <c r="I203" s="19" t="inlineStr">
         <is>
           <t>でも…それだけじゃない！
 丸太先生は加工することで
 さらに「厚板」へと進化するの。</t>
         </is>
       </c>
-      <c r="J202" s="19" t="inlineStr">
+      <c r="J203" s="19" t="inlineStr">
         <is>
           <t>But... that’s not all!
 By processing Mr. Log, you can upgrade it into "Planks".</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Mas isso não é tudo!
-Ao processar o Sr. Tronco, você pode transformá-lo em "Tábuas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H203" s="15" t="n">
+      <c r="K203" s="15" t="inlineStr">
+        <is>
+          <t>Mas... não é tudo!
+Processando o Sr. Tronco, você o melhora para "Tábuas".</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H204" s="15" t="n">
         <v>108</v>
       </c>
-      <c r="I203" s="19" t="inlineStr">
+      <c r="I204" s="19" t="inlineStr">
         <is>
           <t>え…？どうやったら加工できる？
 そうね、丸太先生に聞いてみたらどう？
 ヒントは「加工設備」よ。</t>
         </is>
       </c>
-      <c r="J203" s="19" t="inlineStr">
+      <c r="J204" s="19" t="inlineStr">
         <is>
           <t>Huh...? How do you process it?
 Well, why don't you ask Mr. Log yourself?
 The hint is 'processing equipment'.</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>O quê? Como você processa isso?
-Bem, por que você mesmo não pergunta ao Sr. Tronco?
-A dica é “ processando equipamentos”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H204" s="15" t="n">
+      <c r="K204" s="15" t="inlineStr">
+        <is>
+          <t>Hã...? Como processa?
+Bom, por que não pergunta ao próprio Sr. Tronco?
+A dica é 'equipamento de processamento'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H205" s="15" t="n">
         <v>109</v>
       </c>
-      <c r="I204" s="19" t="inlineStr">
+      <c r="I205" s="19" t="inlineStr">
         <is>
           <t>…ちなみに、石も「切り石」に加工できるから
 覚えておいてね。</t>
         </is>
       </c>
-      <c r="J204" s="19" t="inlineStr">
+      <c r="J205" s="19" t="inlineStr">
         <is>
           <t>...Oh, and by the way, you can also process stones
 into "Cut Stone", so keep that in mind too.</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>... Ah, e a propósito, você também pode processar pedras em “Pedra Cortada”, portanto, lembre-se disso também.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B205" s="19" t="inlineStr">
+      <c r="K205" s="15" t="inlineStr">
+        <is>
+          <t>...Ah, e aliás, você também pode processar pedras
+em "Pedra Talhada", então anote isso também.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B206" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A206" s="19" t="inlineStr">
+    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A207" s="19" t="inlineStr">
         <is>
           <t>hardness</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H208" s="15" t="n">
+    <row r="208" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="209" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H209" s="15" t="n">
         <v>110</v>
       </c>
-      <c r="I208" s="19" t="inlineStr">
+      <c r="I209" s="19" t="inlineStr">
         <is>
           <t>よしよ～し、道具を作ったのね。</t>
         </is>
       </c>
-      <c r="J208" s="25" t="inlineStr">
+      <c r="J209" s="25" t="inlineStr">
         <is>
           <t>Good, you made a tool!</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>Muito bem, você criou uma ferramenta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H209" s="15" t="n">
+      <c r="K209" s="15" t="inlineStr">
+        <is>
+          <t>Boa, você fez uma ferramenta!</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H210" s="15" t="n">
         <v>111</v>
       </c>
-      <c r="I209" s="19" t="inlineStr">
+      <c r="I210" s="19" t="inlineStr">
         <is>
           <t>全てのアイテムは、何らかの「素材」からできている。
 そして、「素材」にはそれぞれ特徴があるの。</t>
         </is>
       </c>
-      <c r="J209" s="25" t="inlineStr">
+      <c r="J210" s="25" t="inlineStr">
         <is>
           <t>All items are made from some kind of "material".
 And each material has its own characteristics.</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Todos os itens são feitos de algum tipo de “material”.
+      <c r="K210" s="15" t="inlineStr">
+        <is>
+          <t>Todos os itens são feitos de algum tipo de "material".
 E cada material tem suas próprias características.</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H210" s="15" t="n">
+    <row r="211" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H211" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="I210" s="19" t="inlineStr">
+      <c r="I211" s="19" t="inlineStr">
         <is>
           <t>例えば紙でできたアイテムは軽かったり
 鉄でできたアイテムは、重いけど燃えにくかったりってね。</t>
         </is>
       </c>
-      <c r="J210" s="25" t="inlineStr">
+      <c r="J211" s="25" t="inlineStr">
         <is>
           <t>For example, items made of paper are light,
 while items made of iron are heavy but hard to burn.</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Por exemplo, itens feitos de papel são leves,
-enquanto itens feitos de ferro são pesados, mas difíceis de queimar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="46.25" customFormat="1" customHeight="1" s="15">
-      <c r="H211" s="15" t="n">
+      <c r="K211" s="15" t="inlineStr">
+        <is>
+          <t>Por exemplo, itens de papel são leves,
+ enquanto itens de ferro são pesados mas difíceis de queimar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="46.25" customFormat="1" customHeight="1" s="15">
+      <c r="H212" s="15" t="n">
         <v>113</v>
       </c>
-      <c r="I211" s="19" t="inlineStr">
+      <c r="I212" s="19" t="inlineStr">
         <is>
           <t>素材の特徴の一つに「硬さ」というものがあって
 特につるはしのような道具では
@@ -5910,7 +5974,7 @@
 この「硬さ」が重要になってくるの。</t>
         </is>
       </c>
-      <c r="J211" s="25" t="inlineStr">
+      <c r="J212" s="25" t="inlineStr">
         <is>
           <t>One of the characteristics of materials is "hardness",
 which is especially important for tools like pickaxes.
@@ -5918,147 +5982,151 @@
 so this "hardness" is very crucial.</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Uma das características dos materiais é a “dureza”, que é especialmente importante para ferramentas como picaretas.
-A dureza do material determina o tipo de pedra ou minério que você pode minerar, portanto, essa "dureza" é muito importante.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H212" s="15" t="n">
+      <c r="K212" s="15" t="inlineStr">
+        <is>
+          <t>Uma das características dos materiais é a "dureza",
+que é especialmente importante para ferramentas como picaretas.
+A dureza do material determina que tipo de pedra ou minério você consegue minerar,
+então essa "dureza" é crucial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H213" s="15" t="n">
         <v>114</v>
       </c>
-      <c r="I212" s="19" t="inlineStr">
+      <c r="I213" s="19" t="inlineStr">
         <is>
           <t>もし今のつるはしで掘れない石が出てきたら
 もっと硬い素材でつるはしを作り直してみるといいわ。</t>
         </is>
       </c>
-      <c r="J212" s="25" t="inlineStr">
+      <c r="J213" s="25" t="inlineStr">
         <is>
           <t>If you come across stones that your current pickaxe can’t mine,
 try making a new pickaxe with a harder material.</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Se você encontrar pedras que sua picareta atual não consegue minerar,
-tente criar uma nova picareta com um material mais duro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="23.85" customHeight="1" s="17">
-      <c r="H213" s="15" t="n">
+      <c r="K213" s="15" t="inlineStr">
+        <is>
+          <t>Se você encontrar pedras que sua picareta atual não minera,
+tente fazer uma picareta nova com um material mais duro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="23.85" customHeight="1" s="17">
+      <c r="H214" s="15" t="n">
         <v>115</v>
       </c>
-      <c r="I213" s="19" t="inlineStr">
+      <c r="I214" s="19" t="inlineStr">
         <is>
           <t>まあ…採掘のスキルを上げまくって
 力ずくで掘っちゃってもいいんだけどね。</t>
         </is>
       </c>
-      <c r="J213" s="25" t="inlineStr">
+      <c r="J214" s="25" t="inlineStr">
         <is>
           <t>Well... you can actually level up your mining skills a lot and
 just power through it, but anyway, hehe.</t>
         </is>
       </c>
-      <c r="K213" s="15" t="inlineStr">
-        <is>
-          <t>Bem... na verdade, você pode aumentar muito o nível de suas habilidades de mineração e simplesmente ignorar isso, mas, de qualquer forma, hehe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B214" s="19" t="inlineStr">
+      <c r="K214" s="15" t="inlineStr">
+        <is>
+          <t>Bem... na verdade, dá para subir muito a perícia de mineração e
+forçar a barra, mas enfim, hehe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B215" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B215" s="19" t="n"/>
-    </row>
-    <row r="216" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="A216" s="19" t="inlineStr">
+    <row r="216" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B216" s="19" t="n"/>
+    </row>
+    <row r="217" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="A217" s="19" t="inlineStr">
         <is>
           <t>middle_click</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H218" s="15" t="n">
+    <row r="218" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="219" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H219" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="I218" s="19" t="inlineStr">
+      <c r="I219" s="19" t="inlineStr">
         <is>
           <t>よしよし、作業台を作れたのね。</t>
         </is>
       </c>
-      <c r="J218" s="25" t="inlineStr">
+      <c r="J219" s="25" t="inlineStr">
         <is>
           <t>Good, you've made the workbench.</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Ótimo, você fez a bancada de trabalho.</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H219" s="15" t="n">
+      <c r="K219" s="15" t="inlineStr">
+        <is>
+          <t>Boa, você fez a bancada de trabalho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H220" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="I219" s="19" t="inlineStr">
+      <c r="I220" s="19" t="inlineStr">
         <is>
           <t>キミに一つ重要なことを教えてあげる。
 一人前の冒険者になるためには、絶対覚えなきゃいけないこと…
 そう、「ミドルクリック」よ。</t>
         </is>
       </c>
-      <c r="J219" s="19" t="inlineStr">
+      <c r="J220" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Let me tell you something crucial for becoming a seasoned adventurer...
 Yes, it's the 'middle click'. </t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Vou lhe dizer algo crucial para se tornar um aventureiro experiente...
-Sim, é o “clique do meio”.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H220" s="15" t="n">
+      <c r="K220" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deixe-me contar algo crucial para virar um aventureiro experiente...
+Sim, é o 'clique do meio'. </t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H221" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="I220" s="19" t="inlineStr">
+      <c r="I221" s="19" t="inlineStr">
         <is>
           <t>バックパックのアイテムや、マップ上の生物やアイテムは
 ミドルクリックすることで「干渉」することができるの。</t>
         </is>
       </c>
-      <c r="J220" s="19" t="inlineStr">
+      <c r="J221" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">By middle-clicking, you can 'interact' with items in your backpack,
 creatures, or objects on the map. </t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Ao clicar com o botão do meio, você pode “interagir” com itens da mochila, criaturas ou objetos no mapa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
-      <c r="H221" s="15" t="n">
+      <c r="K221" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Com o clique do meio, você 'interage' com itens da mochila,
+criaturas ou objetos do mapa. </t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="64.15000000000001" customFormat="1" customHeight="1" s="15">
+      <c r="H222" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="I221" s="19" t="inlineStr">
+      <c r="I222" s="19" t="inlineStr">
         <is>
           <t>例えば邪魔な生物を蹴って動かしたり
 機械のスイッチを入れたり
@@ -6067,7 +6135,7 @@
 普段できない色々な行動が、ミドルクリックによって解放されるのよ。</t>
         </is>
       </c>
-      <c r="J221" s="19" t="inlineStr">
+      <c r="J222" s="19" t="inlineStr">
         <is>
           <t>You can do various actions like
 kicking away pesky creatures,
@@ -6077,642 +6145,642 @@
 It unleashes a whole range of actions that you can't usually do.</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Você pode realizar várias ações, como
-chutar criaturas incômodas,
-acionar interruptores,
+      <c r="K222" s="15" t="inlineStr">
+        <is>
+          <t>Dá para fazer várias ações como
+chutar criaturas chatas para longe,
+virar interruptores,
 misturar poções,
-ou até mesmo acessar a mochila do seu companheiro.
-Ele libera toda uma gama de ações que você normalmente não pode realizar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H222" s="15" t="n">
+ou até acessar a mochila do companheiro.
+Destrava uma gama inteira de ações que você normalmente não pode fazer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H223" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="I222" s="19" t="inlineStr">
+      <c r="I223" s="19" t="inlineStr">
         <is>
           <t>さらに、家具や壁などを設置する時も
 ミドルクリックすれば、対象物を回転させることができる…
 これを知らない冒険者は、この世界では生きていけないわ。</t>
         </is>
       </c>
-      <c r="J222" s="19" t="inlineStr">
+      <c r="J223" s="19" t="inlineStr">
         <is>
           <t>Moreover, when placing furniture or walls,
 middle-clicking will also let you rotate them...
 Adventurers who don't know this won't survive in this world.</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K223" s="15" t="inlineStr">
         <is>
           <t>Além disso, ao colocar móveis ou paredes,
-clicar com o botão do meio também permitirá que você os gire...
-Os aventureiros que não souberem disso não sobreviverão neste mundo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H223" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="I223" s="19" t="inlineStr">
-        <is>
-          <t>…いい？ ミドルクリック…覚えた？</t>
-        </is>
-      </c>
-      <c r="J223" s="19" t="inlineStr">
-        <is>
-          <t>Middle click... got it...?</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Clique do Meio... Entendeu?
-(Dá pra alterar no menu)</t>
+o clique do meio também permite girá-los...
+Aventureiros que não sabem disso não sobrevivem neste mundo.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H224" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="I224" s="19" t="inlineStr">
+        <is>
+          <t>…いい？ ミドルクリック…覚えた？</t>
+        </is>
+      </c>
+      <c r="J224" s="19" t="inlineStr">
+        <is>
+          <t>Middle click... got it...?</t>
+        </is>
+      </c>
+      <c r="K224" s="15" t="inlineStr">
+        <is>
+          <t>Clique do meio... entendeu...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H225" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="I224" s="19" t="inlineStr">
+      <c r="I225" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J224" s="19" t="inlineStr">
+      <c r="J225" s="19" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K225" s="15" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H225" s="15" t="n">
+    <row r="226" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H226" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="I225" s="19" t="inlineStr">
+      <c r="I226" s="19" t="inlineStr">
         <is>
           <t>そうそう
 ミドルクリックはキーボードの「R」キーでも代用できるからね。</t>
         </is>
       </c>
-      <c r="J225" s="19" t="inlineStr">
+      <c r="J226" s="19" t="inlineStr">
         <is>
           <t>Yes, you can also use the 'R' key on your keyboard
 as a substitute for middle click...</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Ah, você também pode usar a tecla "R" do seu teclado
-como substituto do clique do meio...</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="12.8" customHeight="1" s="17">
-      <c r="H226" s="15" t="n">
+      <c r="K226" s="15" t="inlineStr">
+        <is>
+          <t>Sim, você também pode usar a tecla 'R' do teclado
+como substituta do clique do meio...</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="12.8" customHeight="1" s="17">
+      <c r="H227" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="I226" s="19" t="inlineStr">
+      <c r="I227" s="19" t="inlineStr">
         <is>
           <t>それでは、また…</t>
         </is>
       </c>
-      <c r="J226" s="19" t="inlineStr">
+      <c r="J227" s="19" t="inlineStr">
         <is>
           <t>Well then...I'll see you later...</t>
         </is>
       </c>
-      <c r="K226" s="15" t="inlineStr">
-        <is>
-          <t>Bem, então... Até mais tarde…</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="12.8" customHeight="1" s="17">
-      <c r="B227" s="19" t="inlineStr">
+      <c r="K227" s="15" t="inlineStr">
+        <is>
+          <t>Pois então... até logo...</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="12.8" customHeight="1" s="17">
+      <c r="B228" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K227" s="15" t="n"/>
-    </row>
-    <row r="228" ht="15.65" customHeight="1" s="17"/>
+      <c r="K228" s="15" t="n"/>
+    </row>
     <row r="229" ht="15.65" customHeight="1" s="17"/>
     <row r="230" ht="15.65" customHeight="1" s="17"/>
-    <row r="231" ht="12.8" customHeight="1" s="17">
-      <c r="A231" s="15" t="inlineStr">
+    <row r="231" ht="15.65" customHeight="1" s="17"/>
+    <row r="232" ht="12.8" customHeight="1" s="17">
+      <c r="A232" s="15" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="12.8" customHeight="1" s="17">
-      <c r="H233" s="15" t="n">
+    <row r="234" ht="12.8" customHeight="1" s="17">
+      <c r="H234" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="I233" s="19" t="inlineStr">
+      <c r="I234" s="19" t="inlineStr">
         <is>
           <t>わあ…きのこちょーだい？</t>
         </is>
       </c>
-      <c r="J233" s="25" t="inlineStr">
+      <c r="J234" s="25" t="inlineStr">
         <is>
           <t>Wow... Can I have some mushrooms?</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Nossa! Posso comer alguns cogumelos?</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="12.8" customHeight="1" s="17">
-      <c r="B234" s="15" t="inlineStr">
-        <is>
-          <t>food2</t>
-        </is>
-      </c>
-      <c r="D234" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H234" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="I234" s="19" t="inlineStr">
-        <is>
-          <t>ああ</t>
-        </is>
-      </c>
-      <c r="J234" s="25" t="inlineStr">
-        <is>
-          <t>Yes.</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Sim.</t>
+      <c r="K234" s="15" t="inlineStr">
+        <is>
+          <t>Nossa... Posso ficar com alguns cogumelos?</t>
         </is>
       </c>
     </row>
     <row r="235" ht="12.8" customHeight="1" s="17">
       <c r="B235" s="15" t="inlineStr">
         <is>
+          <t>food2</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="H235" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I235" s="19" t="inlineStr">
+        <is>
+          <t>ああ</t>
+        </is>
+      </c>
+      <c r="J235" s="25" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="K235" s="15" t="inlineStr">
+        <is>
+          <t>Sim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="12.8" customHeight="1" s="17">
+      <c r="B236" s="15" t="inlineStr">
+        <is>
           <t>food3</t>
         </is>
       </c>
-      <c r="D235" s="15" t="inlineStr">
+      <c r="D236" s="15" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="H235" s="15" t="n">
+      <c r="H236" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="I235" s="19" t="inlineStr">
+      <c r="I236" s="19" t="inlineStr">
         <is>
           <t>いや</t>
         </is>
       </c>
-      <c r="J235" s="25" t="inlineStr">
+      <c r="J236" s="25" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K236" s="15" t="inlineStr">
         <is>
           <t>Não.</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="12.8" customHeight="1" s="17">
-      <c r="I236" s="19" t="n"/>
-      <c r="J236" s="25" t="n"/>
-    </row>
     <row r="237" ht="12.8" customHeight="1" s="17">
-      <c r="A237" s="15" t="inlineStr">
-        <is>
-          <t>food2</t>
-        </is>
-      </c>
       <c r="I237" s="19" t="n"/>
       <c r="J237" s="25" t="n"/>
     </row>
-    <row r="238" ht="22.35" customHeight="1" s="17">
-      <c r="H238" s="15" t="n">
+    <row r="238" ht="12.8" customHeight="1" s="17">
+      <c r="A238" s="15" t="inlineStr">
+        <is>
+          <t>food2</t>
+        </is>
+      </c>
+      <c r="I238" s="19" t="n"/>
+      <c r="J238" s="25" t="n"/>
+    </row>
+    <row r="239" ht="22.35" customHeight="1" s="17">
+      <c r="H239" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="I238" s="19" t="inlineStr">
+      <c r="I239" s="19" t="inlineStr">
         <is>
           <t>もぐもぐもぐ。おいしい～。
 これ私の大好物なの。覚えておいてね！</t>
         </is>
       </c>
-      <c r="J238" s="19" t="inlineStr">
+      <c r="J239" s="19" t="inlineStr">
         <is>
           <t>Munch munch munch. Yummy.
 These are my favorite! Remember that, okay?</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>Munch munch munch. Que delícia.
-Estes são os meus favoritos! Lembre-se disso, ok?</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H239" s="15" t="n">
+      <c r="K239" s="15" t="inlineStr">
+        <is>
+          <t>Nhac nhac nhac. Que delícia.
+Estes são meus favoritos! Anota aí, combinado?</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H240" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="I239" s="19" t="inlineStr">
+      <c r="I240" s="19" t="inlineStr">
         <is>
           <t>きのこは美味しいけど、腹持ちがよくないし
 時間がたつと腐ってしまうのが難点ね。</t>
         </is>
       </c>
-      <c r="J239" s="19" t="inlineStr">
+      <c r="J240" s="19" t="inlineStr">
         <is>
           <t>Mushrooms are tasty, but they don't keep you full for long
 and the fact that they spoil over time is a downside.</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Os cogumelos são saborosos, mas não o mantêm saciado por muito tempo
-e o fato de que eles estragam com o tempo é uma desvantagem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="22.35" customHeight="1" s="17">
-      <c r="H240" s="15" t="n">
+      <c r="K240" s="15" t="inlineStr">
+        <is>
+          <t>Cogumelos são gostosos, mas não enchem muito
+e o fato de estragarem com o tempo é um defeito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="22.35" customHeight="1" s="17">
+      <c r="H241" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="I240" s="19" t="inlineStr">
+      <c r="I241" s="19" t="inlineStr">
         <is>
           <t>そう、食べ物はずっと置いておくと腐ってしまうのよ。
 知らなかった？</t>
         </is>
       </c>
-      <c r="J240" s="19" t="inlineStr">
+      <c r="J241" s="19" t="inlineStr">
         <is>
           <t>Yes, food spoils if you leave it out too long.
 You didn't know that?</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Sim, os alimentos estragam se você os deixar no "chão" ou na "bolsa" por muito tempo.
-Você não sabia disso?</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="22.35" customHeight="1" s="17">
-      <c r="H241" s="15" t="n">
+      <c r="K241" s="15" t="inlineStr">
+        <is>
+          <t>Sim, comida estraga se você deixar fora por muito tempo.
+Você não sabia?</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="22.35" customHeight="1" s="17">
+      <c r="H242" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="I241" s="19" t="inlineStr">
+      <c r="I242" s="19" t="inlineStr">
         <is>
           <t>当たり前だけど、腐ったものを食べるとお腹を壊すから
 絶対食べてはだめよ。</t>
         </is>
       </c>
-      <c r="J241" s="19" t="inlineStr">
+      <c r="J242" s="19" t="inlineStr">
         <is>
           <t>Of course, eating spoiled food can make you sick
 so you should never eat it.</t>
         </is>
       </c>
-      <c r="K241" s="15" t="inlineStr">
-        <is>
-          <t>É claro que comer alimentos estragados pode deixá-lo doente, portanto, você nunca deve comê-los.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="22.35" customHeight="1" s="17">
-      <c r="H242" s="15" t="n">
+      <c r="K242" s="15" t="inlineStr">
+        <is>
+          <t>Claro, comer comida estragada pode te deixar doente
+então nunca coma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="22.35" customHeight="1" s="17">
+      <c r="H243" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="I242" s="19" t="inlineStr">
+      <c r="I243" s="19" t="inlineStr">
         <is>
           <t>魚や生ものは特に腐りやすいわね。
 逆に、木の実や調理した食料はかなり日持ちするの。</t>
         </is>
       </c>
-      <c r="J242" s="19" t="inlineStr">
+      <c r="J243" s="19" t="inlineStr">
         <is>
           <t>Fish and raw food spoil especially easily
 but nuts and cooked food can last quite a while.</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Peixes e alimentos crus estragam com facilidade,
-mas nozes e comida cozida duram bastante tempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="32.8" customHeight="1" s="17">
-      <c r="H243" s="15" t="n">
+      <c r="K243" s="15" t="inlineStr">
+        <is>
+          <t>Peixe e comida crua estragam especialmente fácil,
+mas castanhas e comida cozida duram bastante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="32.8" customHeight="1" s="17">
+      <c r="H244" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="I243" s="19" t="inlineStr">
+      <c r="I244" s="19" t="inlineStr">
         <is>
           <t>石臼があれば、キブルみたいな全く腐らない料理も作れるのよ。
 長旅の前には、十分な保存食を用意しておくのが
 冒険者の鉄則ね。</t>
         </is>
       </c>
-      <c r="J243" s="19" t="inlineStr">
+      <c r="J244" s="19" t="inlineStr">
         <is>
           <t>With a millstone, you can even make meals like kibble that never spoil.
 Remember to prepare enough non-perishable food before a long journey.
 It's a golden rule for adventurers.</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Com um Moinho de Pedra, você pode até fazer refeições como ração que nunca estraga.
-Lembre-se de levar comida não perecível suficiente antes de uma longa jornada.
-Essa é uma regra de ouro para aventureiros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="12.8" customHeight="1" s="17">
-      <c r="B244" s="15" t="inlineStr">
+      <c r="K244" s="15" t="inlineStr">
+        <is>
+          <t>Com um moinho, dá até para fazer refeições como ração que nunca estragam.
+Lembre de preparar comida não perecível suficiente antes de uma viagem longa.
+É regra de ouro dos aventureiros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="12.8" customHeight="1" s="17">
+      <c r="B245" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="J244" s="19" t="n"/>
-    </row>
-    <row r="245" ht="12.8" customHeight="1" s="17">
-      <c r="A245" s="15" t="inlineStr">
+      <c r="J245" s="19" t="n"/>
+    </row>
+    <row r="246" ht="12.8" customHeight="1" s="17">
+      <c r="A246" s="15" t="inlineStr">
         <is>
           <t>food3</t>
         </is>
       </c>
-      <c r="J245" s="19" t="n"/>
-    </row>
-    <row r="246" ht="12.8" customHeight="1" s="17">
-      <c r="H246" s="15" t="n">
+      <c r="J246" s="19" t="n"/>
+    </row>
+    <row r="247" ht="12.8" customHeight="1" s="17">
+      <c r="H247" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="I246" s="19" t="inlineStr">
+      <c r="I247" s="19" t="inlineStr">
         <is>
           <t>ケチ！</t>
         </is>
       </c>
-      <c r="J246" s="25" t="inlineStr">
+      <c r="J247" s="25" t="inlineStr">
         <is>
           <t>Cheap!</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Que barato!</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B247" s="15" t="inlineStr">
+      <c r="K247" s="15" t="inlineStr">
+        <is>
+          <t>Barato!</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B248" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A249" s="19" t="inlineStr">
+    <row r="249" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="250" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A250" s="19" t="inlineStr">
         <is>
           <t>tinker</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H250" s="15" t="n">
+    <row r="251" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H251" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="I250" s="19" t="inlineStr">
+      <c r="I251" s="19" t="inlineStr">
         <is>
           <t>わぁ、見てみて、行商人達がいっぱい！
 色んなものを売ってるよ！</t>
         </is>
       </c>
-      <c r="J250" s="25" t="inlineStr">
+      <c r="J251" s="25" t="inlineStr">
         <is>
           <t>Wow, look at all the tinkers!
 They're selling all kinds of things!</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Uau, olha quantos mercadores!_x000D_
-Eles estão vendendo todo tipo de coisa!</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H251" s="15" t="n">
+      <c r="K251" s="15" t="inlineStr">
+        <is>
+          <t>Nossa, olha quantos latoeiros!
+Eles estão vendendo de tudo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H252" s="15" t="n">
         <v>94</v>
       </c>
-      <c r="I251" s="19" t="inlineStr">
+      <c r="I252" s="19" t="inlineStr">
         <is>
           <t>まるで小さな街の一角のようね。
 ほら、あの掲示板
 冒険者向けの依頼も掲載されているみたい。</t>
         </is>
       </c>
-      <c r="J251" s="19" t="inlineStr">
+      <c r="J252" s="19" t="inlineStr">
         <is>
           <t>It's like a little corner of a town.
 Look, that notice board seems to have
 quests for adventurers posted on it.</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>Parece um pequeno canto de uma cidade._x000D_
-Olha, aquele quadro de avisos parece ter_x000D_
-missões para aventureiros postadas nele.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H252" s="15" t="n">
+      <c r="K252" s="15" t="inlineStr">
+        <is>
+          <t>É como um quarteirão de cidade.
+Olhe, aquele quadro de avisos parece ter
+missões para aventureiros postadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H253" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="I252" s="19" t="inlineStr">
+      <c r="I253" s="19" t="inlineStr">
         <is>
           <t>依頼を達成すると、様々な報酬がもらえるから
 掲示板を見かけたらこまめにチェック！
 ★の数が多い依頼は難しいから気を付けて。</t>
         </is>
       </c>
-      <c r="J252" s="19" t="inlineStr">
+      <c r="J253" s="19" t="inlineStr">
         <is>
           <t>Completing quests earns you various rewards,
 so make sure to check the notice board regularly!
 Be careful with quests that have many ★. They're more difficult.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Completar missões rende várias recompensas,_x000D_
-então certifique-se de verificar o quadro de avisos regularmente!_x000D_
-Cuidado com as missões que têm muitas ★. Elas são mais difíceis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H253" s="15" t="n">
+      <c r="K253" s="15" t="inlineStr">
+        <is>
+          <t>Completar missões rende várias recompensas,
+então confira o quadro de avisos regularmente!
+Cuidado com missões com muitas ★. São mais difíceis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H254" s="15" t="n">
         <v>96</v>
       </c>
-      <c r="I253" s="19" t="inlineStr">
+      <c r="I254" s="19" t="inlineStr">
         <is>
           <t>あら、この停泊地、癒し手もいるのね。
 癒し手は状態異常を治療してくれるし、あっちの魔術師は
 未鑑定のアイテムを鑑定してくれるわ…まあ、タダじゃないけどね。</t>
         </is>
       </c>
-      <c r="J253" s="19" t="inlineStr">
+      <c r="J254" s="19" t="inlineStr">
         <is>
           <t>Oh, this camp also has a healer.
 The healer can cure status ailments, and the mage there
 can appraise unidentified items...though it does cost money.</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="K254" s="15" t="inlineStr">
         <is>
           <t>Oh, este acampamento também tem um curandeiro.
-O curandeiro pode curar estados negativos, e o mago ali
-pode avaliar itens não identificados... Mas isso custa dinheiro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H254" s="15" t="n">
-        <v>97</v>
-      </c>
-      <c r="I254" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J254" s="19" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>...</t>
+O curandeiro cura estados, e a maga do local
+pode avaliar itens não identificados... embora custe dinheiro.</t>
         </is>
       </c>
     </row>
     <row r="255" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H255" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="I255" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J255" s="19" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K255" s="15" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H256" s="15" t="n">
         <v>98</v>
       </c>
-      <c r="I255" s="19" t="inlineStr">
+      <c r="I256" s="19" t="inlineStr">
         <is>
           <t>あのキャラバンの隊長…</t>
         </is>
       </c>
-      <c r="J255" s="19" t="inlineStr">
+      <c r="J256" s="19" t="inlineStr">
         <is>
           <t>That caravan leader...</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Aquele líder da caravana...</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H256" s="15" t="n">
+      <c r="K256" s="15" t="inlineStr">
+        <is>
+          <t>Aquele líder de caravana...</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H257" s="15" t="n">
         <v>99</v>
       </c>
-      <c r="I256" s="19" t="inlineStr">
+      <c r="I257" s="19" t="inlineStr">
         <is>
           <t>か…かわいい！
 猫のかぶりものをかぶってるわ。
 ねえ、ちょっと寄っていこ？</t>
         </is>
       </c>
-      <c r="J256" s="19" t="inlineStr">
+      <c r="J257" s="19" t="inlineStr">
         <is>
           <t>S...so cute!
 He's wearing a cat costume.
 Hey, let's go check him?</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Tão fofo!
-Ele está vestindo uma fantasia de gato.
-Ei, vamos lá ver ele?</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I257" s="19" t="n"/>
-      <c r="J257" s="19" t="n"/>
+      <c r="K257" s="15" t="inlineStr">
+        <is>
+          <t>T...tão fofo!
+Ele está de fantasia de gato.
+Ei, vamos ver ele?</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B258" s="19" t="inlineStr">
+      <c r="I258" s="19" t="n"/>
+      <c r="J258" s="19" t="n"/>
+    </row>
+    <row r="259" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B259" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A259" s="19" t="inlineStr">
+    <row r="260" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A260" s="19" t="inlineStr">
         <is>
           <t>town</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H260" s="15" t="n">
+    <row r="261" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H261" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="I260" s="19" t="inlineStr">
+      <c r="I261" s="19" t="inlineStr">
         <is>
           <t>街だ～！
 人の往来で辺りに活気があるわね。</t>
         </is>
       </c>
-      <c r="J260" s="25" t="inlineStr">
+      <c r="J261" s="25" t="inlineStr">
         <is>
           <t>It's a town!
 So lively with all the people bustling around.</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K261" s="15" t="inlineStr">
         <is>
           <t>É uma cidade!
-Tão animada com todas as pessoas se movimentando.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H261" s="15" t="n">
+Que agito, todo mundo indo e vindo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H262" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="I261" s="19" t="inlineStr">
+      <c r="I262" s="19" t="inlineStr">
         <is>
           <t>アイテムの売買、訓練、交易、賭博、依頼、回復…
 街には色々なサービスが揃ってる。
@@ -6720,7 +6788,7 @@
 ガードに話しかければ、道案内をしてもらえるわ。えへへ。</t>
         </is>
       </c>
-      <c r="J261" s="19" t="inlineStr">
+      <c r="J262" s="19" t="inlineStr">
         <is>
           <t>Buying and selling, training, trading, gambling, quests, healing...
 There are so many services here.
@@ -6728,149 +6796,150 @@
 Just talk to a guard, and they'll guide you. Hehe.</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Comprar e vender, treinar, negociar, apostar, missões, cura...
+      <c r="K262" s="15" t="inlineStr">
+        <is>
+          <t>Comprar e vender, treinar, trocar, apostar, missões, cura...
 Há tantos serviços aqui.
-Mesmo se você se perder, não se preocupe.
-Basta falar com um guarda, e ele te guiará. Hehe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H262" s="15" t="n">
+Mesmo que se perca, não se preocupe.
+Só fale com um guarda, e eles guiam você. Hehe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H263" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="I262" s="19" t="inlineStr">
+      <c r="I263" s="19" t="inlineStr">
         <is>
           <t>当然だけど、ノースティリスにある街は
 街ごとに発展度も違えば、売っている物も
 受けられるサービスも、訓練できるスキルも違うの。</t>
         </is>
       </c>
-      <c r="J262" s="19" t="inlineStr">
+      <c r="J263" s="19" t="inlineStr">
         <is>
           <t>Of course, every town in North Tyris is different.
 They vary in development, the items they sell,
 the services they offer, and the skills you can train.</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Claro, cada cidade em North Tyris é diferente.
-Elas variam no desenvolvimento, nos itens que vendem,
-nos serviços que oferecem e nas habilidades que você pode treinar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H263" s="15" t="n">
+      <c r="K263" s="15" t="inlineStr">
+        <is>
+          <t>Claro, cada cidade de Tyris do Norte é diferente.
+Elas variam em desenvolvimento, nos itens que vendem,
+nos serviços que oferecem e nas perícias que se pode treinar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H264" s="15" t="n">
         <v>103</v>
       </c>
-      <c r="I263" s="19" t="inlineStr">
+      <c r="I264" s="19" t="inlineStr">
         <is>
           <t>掲示板に掲載される依頼も、街によって傾向が異なるから
 色んな街を巡ってみるのもいいわね。</t>
         </is>
       </c>
-      <c r="J263" s="19" t="inlineStr">
+      <c r="J264" s="19" t="inlineStr">
         <is>
           <t>The quests posted on the bulletin board also differ from one to another,
 so it will be a good idea to explore various towns.</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>As missões postadas no quadro de avisos também diferem de uma cidade para outra, então pode ser uma boa ideia explorar várias cidades.</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H264" s="15" t="n">
+      <c r="K264" s="15" t="inlineStr">
+        <is>
+          <t>As missões postadas no quadro de avisos também variam de uma para outra,
+então vai ser boa ideia explorar várias cidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H265" s="15" t="n">
         <v>104</v>
       </c>
-      <c r="I264" s="19" t="inlineStr">
+      <c r="I265" s="19" t="inlineStr">
         <is>
           <t>今はともかく、この街を探索してみましょ？</t>
         </is>
       </c>
-      <c r="J264" s="19" t="inlineStr">
+      <c r="J265" s="19" t="inlineStr">
         <is>
           <t>But, for now, how about we explore this town?</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Mas, por enquanto, que tal explorarmos essa cidade?</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="I265" s="19" t="n"/>
-      <c r="J265" s="19" t="n"/>
+      <c r="K265" s="15" t="inlineStr">
+        <is>
+          <t>Mas, por ora, que tal explorarmos esta cidade?</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B266" s="19" t="inlineStr">
+      <c r="I266" s="19" t="n"/>
+      <c r="J266" s="19" t="n"/>
+    </row>
+    <row r="267" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B267" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B267" s="19" t="n"/>
-    </row>
     <row r="268" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A268" s="19" t="inlineStr">
+      <c r="B268" s="19" t="n"/>
+    </row>
+    <row r="269" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A269" s="19" t="inlineStr">
         <is>
           <t>karma</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H269" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="I269" s="19" t="inlineStr">
-        <is>
-          <t>…</t>
-        </is>
-      </c>
-      <c r="J269" s="25" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>...</t>
         </is>
       </c>
     </row>
     <row r="270" ht="12.8" customFormat="1" customHeight="1" s="15">
       <c r="H270" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="I270" s="19" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="J270" s="25" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="K270" s="15" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H271" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="I270" s="19" t="inlineStr">
+      <c r="I271" s="19" t="inlineStr">
         <is>
           <t>今、悪いことしたでしょ…？</t>
         </is>
       </c>
-      <c r="J270" s="19" t="inlineStr">
+      <c r="J271" s="19" t="inlineStr">
         <is>
           <t>Did you just do something bad...?</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Você acabou de fazer algo ruim?</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H271" s="15" t="n">
+      <c r="K271" s="15" t="inlineStr">
+        <is>
+          <t>Você acabou de fazer algo ruim...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H272" s="15" t="n">
         <v>81</v>
       </c>
-      <c r="I271" s="19" t="inlineStr">
+      <c r="I272" s="19" t="inlineStr">
         <is>
           <t>ええ…キミのカルマが下がるのを感じたのよ。
 この世界では、悪いことをするとカルマが下がって
@@ -6878,7 +6947,7 @@
 …犯罪者になると、生きていくのが大変よ。</t>
         </is>
       </c>
-      <c r="J271" s="19" t="inlineStr">
+      <c r="J272" s="19" t="inlineStr">
         <is>
           <t>Yes... I felt your karma drop.
 In this world, your karma decreases if you do bad things,
@@ -6886,43 +6955,43 @@
 ... Becoming a criminal makes life very difficult.</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Sim... Eu senti seu carma cair.
-Neste mundo, seu carma diminui se você fizer coisas ruins,
-e se cair abaixo de zero, você se torna um criminoso.
-... Tornar-se um criminoso torna a vida muito difícil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H272" s="15" t="n">
+      <c r="K272" s="15" t="inlineStr">
+        <is>
+          <t>Sim... Senti seu karma cair.
+Neste mundo, seu karma diminui se você fizer coisas ruins,
+e se cair abaixo de zero, você vira criminal.
+... Virar criminal deixa a vida bem difícil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H273" s="15" t="n">
         <v>82</v>
       </c>
-      <c r="I272" s="19" t="inlineStr">
+      <c r="I273" s="19" t="inlineStr">
         <is>
           <t>依頼をこなしたり、落とし物を届けたり
 日ごろから善い行いを心がけて、カルマを高めていってね。</t>
         </is>
       </c>
-      <c r="J272" s="19" t="inlineStr">
+      <c r="J273" s="19" t="inlineStr">
         <is>
           <t>Complete quests, return lost items,
 and always strive to do good deeds to increase your karma.</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Complete missões, devolva itens perdidos,
-e sempre se esforce para fazer boas ações para aumentar seu carma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H273" s="15" t="n">
+      <c r="K273" s="15" t="inlineStr">
+        <is>
+          <t>Complete missões, devolva itens perdidos
+e sempre procure fazer boas ações para subir seu karma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H274" s="15" t="n">
         <v>83</v>
       </c>
-      <c r="I273" s="19" t="inlineStr">
+      <c r="I274" s="19" t="inlineStr">
         <is>
           <t>…ちなみに
 この世界で最も重い罪は税金の滞納よ。
@@ -6930,144 +6999,144 @@
 命を狙われるようになるわ。</t>
         </is>
       </c>
-      <c r="J273" s="19" t="inlineStr">
+      <c r="J274" s="19" t="inlineStr">
         <is>
           <t>...By the way, the most serious crime in this world is tax evasion.
 If you don’t pay your taxes for four months,
 you’ll be immediately wanted, and your life will be in danger.</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>... A propósito, o crime mais grave do mundo é a sonegação de impostos.
+      <c r="K274" s="15" t="inlineStr">
+        <is>
+          <t>...Aliás, o crime mais sério deste mundo é sonegar imposto.
 Se você não pagar seus impostos por quatro meses,
-você será imediatamente procurado e sua vida correrá perigo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H274" s="15" t="n">
+você vira procurado na hora, e sua vida fica em risco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H275" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="I274" s="19" t="inlineStr">
+      <c r="I275" s="19" t="inlineStr">
         <is>
           <t>くれぐれも気を付けて…</t>
         </is>
       </c>
-      <c r="J274" s="19" t="inlineStr">
+      <c r="J275" s="19" t="inlineStr">
         <is>
           <t>So...be careful, okay?</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Portanto... Tome cuidado, ok?</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="12.8" customHeight="1" s="17">
-      <c r="I275" s="19" t="n"/>
-      <c r="J275" s="19" t="n"/>
-      <c r="K275" s="15" t="n"/>
+      <c r="K275" s="15" t="inlineStr">
+        <is>
+          <t>Então...cuidado, combinado?</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="12.8" customHeight="1" s="17">
-      <c r="B276" s="19" t="inlineStr">
+      <c r="I276" s="19" t="n"/>
+      <c r="J276" s="19" t="n"/>
+      <c r="K276" s="15" t="n"/>
+    </row>
+    <row r="277" ht="12.8" customHeight="1" s="17">
+      <c r="B277" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K276" s="15" t="n"/>
-    </row>
-    <row r="277" ht="12.8" customHeight="1" s="17">
-      <c r="B277" s="19" t="n"/>
       <c r="K277" s="15" t="n"/>
     </row>
     <row r="278" ht="12.8" customHeight="1" s="17">
-      <c r="A278" s="19" t="inlineStr">
+      <c r="B278" s="19" t="n"/>
+      <c r="K278" s="15" t="n"/>
+    </row>
+    <row r="279" ht="12.8" customHeight="1" s="17">
+      <c r="A279" s="19" t="inlineStr">
         <is>
           <t>criminal</t>
         </is>
       </c>
-      <c r="K278" s="15" t="n"/>
-    </row>
-    <row r="279" ht="12.8" customHeight="1" s="17">
-      <c r="H279" s="15" t="n">
+      <c r="K279" s="15" t="n"/>
+    </row>
+    <row r="280" ht="12.8" customHeight="1" s="17">
+      <c r="H280" s="15" t="n">
         <v>85</v>
       </c>
-      <c r="I279" s="19" t="inlineStr">
+      <c r="I280" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J279" s="25" t="inlineStr">
+      <c r="J280" s="25" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K279" s="15" t="inlineStr">
+      <c r="K280" s="15" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="22.35" customHeight="1" s="17">
-      <c r="H280" s="15" t="n">
+    <row r="281" ht="22.35" customHeight="1" s="17">
+      <c r="H281" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="I280" s="19" t="inlineStr">
+      <c r="I281" s="19" t="inlineStr">
         <is>
           <t>イヤ…！
 近づかないで、変態！</t>
         </is>
       </c>
-      <c r="J280" s="19" t="inlineStr">
+      <c r="J281" s="19" t="inlineStr">
         <is>
           <t>No...!
 Stay away from me, you pervert!</t>
         </is>
       </c>
-      <c r="K280" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não...!  _x000D_
-Fique longe de mim, seu pervertido!  </t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="22.35" customHeight="1" s="17">
-      <c r="H281" s="15" t="n">
+      <c r="K281" s="15" t="inlineStr">
+        <is>
+          <t>Não...!
+Fique longe de mim, seu pervertido!</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="22.35" customHeight="1" s="17">
+      <c r="H282" s="15" t="n">
         <v>87</v>
       </c>
-      <c r="I281" s="19" t="inlineStr">
+      <c r="I282" s="19" t="inlineStr">
         <is>
           <t>犯罪者に身を堕としてしまうなんて、
 キミのことを見損なったわ。</t>
         </is>
       </c>
-      <c r="J281" s="19" t="inlineStr">
+      <c r="J282" s="19" t="inlineStr">
         <is>
           <t>I can't believe you've become a criminal.
 I'm really disappointed in you.</t>
         </is>
       </c>
-      <c r="K281" s="15" t="inlineStr">
-        <is>
-          <t>Não acredito que você tenha se tornado um criminoso.
-Estou muito decepcionada com você.</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="43.25" customHeight="1" s="17">
-      <c r="H282" s="15" t="n">
+      <c r="K282" s="15" t="inlineStr">
+        <is>
+          <t>Não acredito que você virou criminal.
+Estou realmente decepcionada com você.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="43.25" customHeight="1" s="17">
+      <c r="H283" s="15" t="n">
         <v>88</v>
       </c>
-      <c r="I282" s="19" t="inlineStr">
+      <c r="I283" s="19" t="inlineStr">
         <is>
           <t>…そう、カルマが0を下回ると、キミは指名手配されてしまう。
 ガードから追いかけられ、商人との取引も断られ、妹達から白い目で見られ
 社会の敵として、一生みじめに暮らすのよ！</t>
         </is>
       </c>
-      <c r="J282" s="19" t="inlineStr">
+      <c r="J283" s="19" t="inlineStr">
         <is>
           <t>…That's right, if your karma drops below zero, you'll be wanted.
 Guards will come chasing you, merchants will refuse to trade with you,
@@ -7075,180 +7144,180 @@
 You'll live a miserable life as an enemy of society!</t>
         </is>
       </c>
-      <c r="K282" s="15" t="inlineStr">
-        <is>
-          <t>... É isso mesmo, se o seu carma cair abaixo de zero, você será procurado.
-Os guardas virão atrás de você, os comerciantes se recusarão a negociar com você,
-e até mesmo suas irmãs olharão para você com desdém.
-Você viverá uma vida miserável como um inimigo da sociedade!</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="32.8" customHeight="1" s="17">
-      <c r="H283" s="15" t="n">
+      <c r="K283" s="15" t="inlineStr">
+        <is>
+          <t>…Pois é: se seu karma cair abaixo de zero, você vira procurado.
+Os guardas vêm atrás de você, os mercadores se recusam a negociar,
+e até suas irmãs te olham com desdém.
+Você viverá uma vida miserável como inimigo da sociedade!</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="32.8" customHeight="1" s="17">
+      <c r="H284" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="I283" s="19" t="inlineStr">
+      <c r="I284" s="19" t="inlineStr">
         <is>
           <t>はぁ…大丈夫、キミにもまだ、更生の道は残されているわ。
 カルマがマイナスの時、カルマは少しずつ上昇していくの。
 悪事を止めて、大人しく待っていれば、いつかはほとぼりも冷める…</t>
         </is>
       </c>
-      <c r="J283" s="19" t="inlineStr">
+      <c r="J284" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Sigh... It's okay, there's still a path to redemption for you.
 When your karma is negative, it will slowly increase over time.
 If you stop committing crimes and patiently wait, things will eventually calm down. </t>
         </is>
       </c>
-      <c r="K283" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*suspiro* - Tudo bem, ainda há um caminho para a redenção.  
-Quando seu carma for negativo, ele aumentará lentamente com o tempo.  
-Se você parar de cometer crimes e esperar pacientemente, as coisas eventualmente se acalmarão.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="22.35" customHeight="1" s="17">
-      <c r="H284" s="15" t="n">
+      <c r="K284" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ufa... Tudo bem, ainda há um caminho de redenção para você.
+Quando seu karma está negativo, ele sobe devagar com o tempo.
+Se parar de cometer crimes e esperar com paciência, as coisas se acalmam eventualmente. </t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="22.35" customHeight="1" s="17">
+      <c r="H285" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="I284" s="19" t="inlineStr">
+      <c r="I285" s="19" t="inlineStr">
         <is>
           <t>法律が存在しない、ならず者たちの街ダルフィなら
 税金を納めることもできるし、商人も取引をしてくれるわ。</t>
         </is>
       </c>
-      <c r="J284" s="19" t="inlineStr">
+      <c r="J285" s="19" t="inlineStr">
         <is>
           <t>In the rogue town of Derphy, where there are no laws,
 you can pay your taxes, and merchants will still trade with you.</t>
         </is>
       </c>
-      <c r="K284" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Na cidade dos foras da lei, Derphy, onde não há leis,  _x000D_
-você pode pagar seus impostos, e os mercadores ainda negociarão com você.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="22.35" customHeight="1" s="17">
-      <c r="H285" s="15" t="n">
+      <c r="K285" s="15" t="inlineStr">
+        <is>
+          <t>Na cidade de ladrões de Derphy, onde não há leis,
+você pode pagar seus impostos, e os mercadores ainda negociam com você.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="22.35" customHeight="1" s="17">
+      <c r="H286" s="15" t="n">
         <v>91</v>
       </c>
-      <c r="I285" s="19" t="inlineStr">
+      <c r="I286" s="19" t="inlineStr">
         <is>
           <t>大丈夫、キミのこと信じてるから
 しっかり罪を償って戻ってきてね。</t>
         </is>
       </c>
-      <c r="J285" s="19" t="inlineStr">
+      <c r="J286" s="19" t="inlineStr">
         <is>
           <t>Don't worry, I believe in you.
 Make sure you atone for your sins and come back.</t>
         </is>
       </c>
-      <c r="K285" s="15" t="inlineStr">
+      <c r="K286" s="15" t="inlineStr">
         <is>
           <t>Não se preocupe, eu acredito em você.
-Certifique-se de arrepender-se de seus pecados e voltar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="12.8" customHeight="1" s="17">
-      <c r="H286" s="15" t="n">
+Expire seus pecados e volte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="12.8" customHeight="1" s="17">
+      <c r="H287" s="15" t="n">
         <v>92</v>
       </c>
-      <c r="I286" s="19" t="inlineStr">
+      <c r="I287" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J286" s="19" t="inlineStr">
+      <c r="J287" s="19" t="inlineStr">
         <is>
           <t>Until then...</t>
         </is>
       </c>
-      <c r="K286" s="15" t="inlineStr">
+      <c r="K287" s="15" t="inlineStr">
         <is>
           <t>Até lá...</t>
         </is>
       </c>
     </row>
-    <row r="287" ht="12.8" customHeight="1" s="17">
-      <c r="B287" s="19" t="inlineStr">
+    <row r="288" ht="12.8" customHeight="1" s="17">
+      <c r="B288" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K287" s="15" t="n"/>
-    </row>
-    <row r="289" ht="12.8" customHeight="1" s="17">
-      <c r="A289" s="19" t="inlineStr">
+      <c r="K288" s="15" t="n"/>
+    </row>
+    <row r="290" ht="12.8" customHeight="1" s="17">
+      <c r="A290" s="19" t="inlineStr">
         <is>
           <t>ether</t>
         </is>
       </c>
-      <c r="K289" s="15" t="n"/>
-    </row>
-    <row r="290" ht="12.8" customHeight="1" s="17">
-      <c r="H290" s="15" t="n">
+      <c r="K290" s="15" t="n"/>
+    </row>
+    <row r="291" ht="12.8" customHeight="1" s="17">
+      <c r="H291" s="15" t="n">
         <v>74</v>
       </c>
-      <c r="I290" s="19" t="inlineStr">
+      <c r="I291" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">キミもとうとう病におかされてしまったのね… </t>
         </is>
       </c>
-      <c r="J290" s="25" t="inlineStr">
+      <c r="J291" s="25" t="inlineStr">
         <is>
           <t>So, you've finally been afflicted by the illness...</t>
         </is>
       </c>
-      <c r="K290" s="15" t="inlineStr">
-        <is>
-          <t>Você finalmente ficou doente...</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="32.8" customHeight="1" s="17">
-      <c r="H291" s="15" t="n">
+      <c r="K291" s="15" t="inlineStr">
+        <is>
+          <t>Oh... Então foi afligido pela doença...</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="32.8" customHeight="1" s="17">
+      <c r="H292" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="I291" s="19" t="inlineStr">
+      <c r="I292" s="19" t="inlineStr">
         <is>
           <t>驚かないでいいの。
 何もしないでも、エーテルの侵食は時間と供に緩やかに進んでいくのよ。</t>
         </is>
       </c>
-      <c r="J291" s="19" t="inlineStr">
+      <c r="J292" s="19" t="inlineStr">
         <is>
           <t>Don't be surprised.
 Even if you do nothing, the ether's encroachment
 will gradually progress over time.</t>
         </is>
       </c>
-      <c r="K291" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não fique surpreso.  
-Mesmo que você não faça nada, a invasão do éter  
-vai progredir gradualmente com o tempo.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="43.25" customHeight="1" s="17">
-      <c r="H292" s="15" t="n">
+      <c r="K292" s="15" t="inlineStr">
+        <is>
+          <t>Não se surpreenda.
+Mesmo que você não faça nada, o avanço do éter
+vai progredindo gradualmente com o tempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="43.25" customHeight="1" s="17">
+      <c r="H293" s="15" t="n">
         <v>76</v>
       </c>
-      <c r="I292" s="19" t="inlineStr">
+      <c r="I293" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">キミの症状はまだまだ無視してかまわない程度だけど
 病気を放っておくと、症状はどんどん悪化して最後には死んじゃうの。
 …病を遅らせる何らかの方法を見つけなくてはね。 </t>
         </is>
       </c>
-      <c r="J292" s="19" t="inlineStr">
+      <c r="J293" s="19" t="inlineStr">
         <is>
           <t>Your symptoms are still minor and can be ignored for now,
 but if you leave the illness untreated,
@@ -7256,317 +7325,319 @@
 ...We need to find some way to slow down the disease.</t>
         </is>
       </c>
-      <c r="K292" s="15" t="inlineStr">
-        <is>
-          <t>Seus sintomas ainda são leves e podem ser ignorados por enquanto,
-mas se você deixar a doença sem tratamento,
-os sintomas se agravarão e, eventualmente, você morrerá.
-... Precisamos encontrar alguma forma de desacelerar a doença.</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="22.35" customHeight="1" s="17">
-      <c r="H293" s="15" t="n">
+      <c r="K293" s="15" t="inlineStr">
+        <is>
+          <t>Seus sintomas ainda são leves e podem ser ignorados por ora,
+mas se deixar a doença sem tratamento,
+eles pioram e no fim você morre.
+...Precisamos achar um jeito de desacelerar a doença.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="22.35" customHeight="1" s="17">
+      <c r="H294" s="15" t="n">
         <v>77</v>
       </c>
-      <c r="I293" s="19" t="inlineStr">
+      <c r="I294" s="19" t="inlineStr">
         <is>
           <t>えへへ、そんなに心配しなくても大丈夫よ。
 時間はたっぷりあるんだから、何か解決策を見つけましょ？</t>
         </is>
       </c>
-      <c r="J293" s="19" t="inlineStr">
+      <c r="J294" s="19" t="inlineStr">
         <is>
           <t>Hehe, don't make that serious face.
 We have plenty of time, so let's find a solution, okay?</t>
         </is>
       </c>
-      <c r="K293" s="15" t="inlineStr">
-        <is>
-          <t>Heh heh, não se preocupe tanto.
-Temos muito tempo para encontrar uma solução.</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="32.8" customHeight="1" s="17">
-      <c r="H294" s="15" t="n">
+      <c r="K294" s="15" t="inlineStr">
+        <is>
+          <t>Hehe, não faça essa cara séria.
+Temos tempo de sobra, então vamos achar uma solução, combinado?</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="32.8" customHeight="1" s="17">
+      <c r="H295" s="15" t="n">
         <v>78</v>
       </c>
-      <c r="I294" s="19" t="inlineStr">
+      <c r="I295" s="19" t="inlineStr">
         <is>
           <t>そういえば、ノイエル南にある雪原の工房で
 奇妙なアイテムを収集している丘の民がいたわね。
 彼ならもしかしたら…</t>
         </is>
       </c>
-      <c r="J294" s="19" t="inlineStr">
+      <c r="J295" s="19" t="inlineStr">
         <is>
           <t>Come to think of it...
 There was a hillfolk in a workshop south of Noyel
 who was collecting strange items. Maybe he could...</t>
         </is>
       </c>
-      <c r="K294" s="15" t="inlineStr">
+      <c r="K295" s="15" t="inlineStr">
         <is>
           <t>Pensando bem...
-Havia um habitante da colina em uma oficina ao sul de Noyel
-que estava coletando itens estranhos. Talvez ele pudesse…</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="12.8" customHeight="1" s="17">
-      <c r="I295" s="19" t="n"/>
-      <c r="J295" s="19" t="n"/>
-      <c r="K295" s="15" t="n"/>
+Havia um povo das colinas numa oficina ao sul de Noyel
+que colecionava itens estranhos. Talvez ele possa...</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="12.8" customHeight="1" s="17">
       <c r="I296" s="19" t="n"/>
       <c r="J296" s="19" t="n"/>
       <c r="K296" s="15" t="n"/>
     </row>
-    <row r="297" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B297" s="19" t="inlineStr">
+    <row r="297" ht="12.8" customHeight="1" s="17">
+      <c r="I297" s="19" t="n"/>
+      <c r="J297" s="19" t="n"/>
+      <c r="K297" s="15" t="n"/>
+    </row>
+    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B298" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A299" s="19" t="inlineStr">
+    <row r="299" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="300" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A300" s="19" t="inlineStr">
         <is>
           <t>faith</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H300" s="15" t="n">
+    <row r="301" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H301" s="15" t="n">
         <v>66</v>
       </c>
-      <c r="I300" s="19" t="inlineStr">
+      <c r="I301" s="19" t="inlineStr">
         <is>
           <t>え、神を信仰した…？
 うふふ…</t>
         </is>
       </c>
-      <c r="J300" s="25" t="inlineStr">
+      <c r="J301" s="25" t="inlineStr">
         <is>
           <t>Oh, did you start worshipping a god?
 Hehe...</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>O quê, você acreditava em Deus...?
-Uh-huh…</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H301" s="15" t="n">
+      <c r="K301" s="15" t="inlineStr">
+        <is>
+          <t>Oh, você começou a cultuar um deus?
+Hehe...</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H302" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="I301" s="19" t="inlineStr">
+      <c r="I302" s="19" t="inlineStr">
         <is>
           <t>ねえ、教えてよ！誰を信仰したの？
 キミの初信仰の相手は誰？ふふふ。</t>
         </is>
       </c>
-      <c r="J301" s="19" t="inlineStr">
+      <c r="J302" s="19" t="inlineStr">
         <is>
           <t>Come on, tell me! Who did you choose to worship?
 Who's your first god? Hehe.</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Vamos lá, conte-me! Quem você escolheu para adorar?
-Quem é seu primeiro Deus? Hehe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H302" s="15" t="n">
+      <c r="K302" s="15" t="inlineStr">
+        <is>
+          <t>Vamos, conta! Quem você escolheu cultuar?
+Quem é seu primeiro deus? Hehe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H303" s="15" t="n">
         <v>68</v>
       </c>
-      <c r="I302" s="19" t="inlineStr">
+      <c r="I303" s="19" t="inlineStr">
         <is>
           <t>…#god。</t>
         </is>
       </c>
-      <c r="J302" s="19" t="inlineStr">
+      <c r="J303" s="19" t="inlineStr">
         <is>
           <t>...#god.</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...#god.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H303" s="15" t="n">
+      <c r="K303" s="15" t="inlineStr">
+        <is>
+          <t>...#god.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H304" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="I303" s="19" t="inlineStr">
+      <c r="I304" s="19" t="inlineStr">
         <is>
           <t>キミって、やっぱりそういう趣味をしてたのね。
 ふ～ん…</t>
         </is>
       </c>
-      <c r="J303" s="19" t="inlineStr">
+      <c r="J304" s="19" t="inlineStr">
         <is>
           <t>I see, so that's your thing, huh?
 Huh...</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo, então é isso que te interessa, hein?  
-Huh...  </t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H304" s="15" t="n">
+      <c r="K304" s="15" t="inlineStr">
+        <is>
+          <t>Entendi, essa é a sua praia, né?
+Huh...</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H305" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="I304" s="19" t="inlineStr">
+      <c r="I305" s="19" t="inlineStr">
         <is>
           <t>神を信仰すると、信仰の深さによって様々な恩恵が与えられるわ。
 信仰は、捧げものをしたり、時間が経つことで深まっていくの。</t>
         </is>
       </c>
-      <c r="J304" s="19" t="inlineStr">
+      <c r="J305" s="19" t="inlineStr">
         <is>
           <t>When you worship a god, you'll receive various blessings
 depending on the depth of your faith.
 Your faith deepens through offerings and the passage of time.</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Ao adorar um Deus, você receberá várias bênçãos, dependendo da profundidade de sua fé.
-Sua fé se aprofunda com as oferendas e a passagem do tempo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="305" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H305" s="15" t="n">
+      <c r="K305" s="15" t="inlineStr">
+        <is>
+          <t>Quando você cultua um deus, recebe várias bênçãos
+dependo da profundidade da sua fé.
+Sua fé se aprofunda com oferendas e com a passagem do tempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H306" s="15" t="n">
         <v>71</v>
       </c>
-      <c r="I305" s="19" t="inlineStr">
+      <c r="I306" s="19" t="inlineStr">
         <is>
           <t>また、一日に一度だけ、神に「祈る」アビリティを使うこともできる。
 体力が回復したり、神様の機嫌にもよるけど、贈り物を賜ることもあるわ。</t>
         </is>
       </c>
-      <c r="J305" s="19" t="inlineStr">
+      <c r="J306" s="19" t="inlineStr">
         <is>
           <t>Once a day, you can use the "Pray" ability to your god.
 It can restore your health, and depending on the god's mood,
 you might receive a gift.</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uma vez por dia, você pode usar a habilidade "Orar" para seu Deus.  
-Ela pode restaurar sua saúde e, dependendo do humor do Deus, você pode receber um presente.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H306" s="15" t="n">
+      <c r="K306" s="15" t="inlineStr">
+        <is>
+          <t>Uma vez por dia, você pode usar a habilidade "Orar" ao seu deus.
+Ela pode restaurar sua vida e, dependendo do humor do deus,
+você pode ganhar um presente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H307" s="15" t="n">
         <v>72</v>
       </c>
-      <c r="I306" s="19" t="inlineStr">
+      <c r="I307" s="19" t="inlineStr">
         <is>
           <t>「祈る」ことで、キミの信仰スキルも鍛えられるから
 一日に一度は祈ってみるといいわね。</t>
         </is>
       </c>
-      <c r="J306" s="19" t="inlineStr">
+      <c r="J307" s="19" t="inlineStr">
         <is>
           <t>Praying also helps you develop your faith skill,
 so try to pray at least once a day.</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>A oração também o ajuda a desenvolver sua habilidade de fé,
-portanto, tente orar pelo menos uma vez por dia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="307" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H307" s="15" t="n">
+      <c r="K307" s="15" t="inlineStr">
+        <is>
+          <t>Orar também ajuda a desenvolver sua perícia de Fé,
+então tente orar pelo menos uma vez por dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H308" s="15" t="n">
         <v>73</v>
       </c>
-      <c r="I307" s="19" t="inlineStr">
+      <c r="I308" s="19" t="inlineStr">
         <is>
           <t>じゃあ、#godを怒らせないように気を付けてね。</t>
         </is>
       </c>
-      <c r="J307" s="19" t="inlineStr">
+      <c r="J308" s="19" t="inlineStr">
         <is>
           <t>Well, that's it for now.
 Just be careful not to anger #god.</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Bem, por enquanto é isso.
-Apenas tome cuidado para não irritar #god.</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="B308" s="19" t="inlineStr">
+      <c r="K308" s="15" t="inlineStr">
+        <is>
+          <t>Bom, é isso por ora.
+Só cuidado para não irritar #god.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="B309" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A309" s="19" t="inlineStr">
+    <row r="310" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A310" s="19" t="inlineStr">
         <is>
           <t>healer</t>
         </is>
       </c>
     </row>
-    <row r="310" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H310" s="15" t="n">
+    <row r="311" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H311" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="I310" s="19" t="inlineStr">
+      <c r="I311" s="19" t="inlineStr">
         <is>
           <t>あ…キミ、弱くなっちゃったの？</t>
         </is>
       </c>
-      <c r="J310" s="25" t="inlineStr">
+      <c r="J311" s="25" t="inlineStr">
         <is>
           <t>Oh... Have you become weaker?</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="K311" s="15" t="inlineStr">
         <is>
           <t>Oh... Você ficou mais fraco?</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H311" s="15" t="n">
+    <row r="312" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H312" s="15" t="n">
         <v>61</v>
       </c>
-      <c r="I311" s="19" t="inlineStr">
+      <c r="I312" s="19" t="inlineStr">
         <is>
           <t>え？どういうことって…
 ちょっと自分の主能力を確認してみてね？
 普段より能力が低下してるでしょ？</t>
         </is>
       </c>
-      <c r="J311" s="19" t="inlineStr">
+      <c r="J312" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">
 What? What do I mean by that... 
@@ -7574,398 +7645,401 @@
 You'll notice they're lower than usual, right?</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  
-O quê? O que quero dizer com isso...  
-Apenas verifique seus atributos principais por um momento, ok?  
-Você vai notar que eles estão mais baixos que o normal, certo?  </t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H312" s="15" t="n">
+      <c r="K312" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Como? O que quero dizer com isso...
+Checa seus atributos primários por um instante, vai.
+Você vai notar que estão mais baixos que o normal, certo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H313" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="I312" s="19" t="inlineStr">
+      <c r="I313" s="19" t="inlineStr">
         <is>
           <t>一部の敵は、キミの能力を弱体化させる攻撃をしてくるの。
 弱体は、最初は問題ないけど、積み重なってくると厄介よ。</t>
         </is>
       </c>
-      <c r="J312" s="19" t="inlineStr">
+      <c r="J313" s="19" t="inlineStr">
         <is>
           <t>Some enemies can weaken your attributes with their attacks.
 At first, it's not a big deal, but if it piles up, it can become troublesome.</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Alguns inimigos podem enfraquecer seus atributos com os ataques deles.
-No início, isso não é um grande problema, mas se acumular, pode se tornar incômodo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H313" s="15" t="n">
+      <c r="K313" s="15" t="inlineStr">
+        <is>
+          <t>Alguns inimigos podem enfraquecer seus atributos com os ataques.
+No começo não é grande coisa, mas se acumular, pode dar problema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H314" s="15" t="n">
         <v>63</v>
       </c>
-      <c r="I313" s="19" t="inlineStr">
+      <c r="I314" s="19" t="inlineStr">
         <is>
           <t>もし肉体復活か精神復活のポーションを持ってるなら
 それを飲めば弱体を回復することができるわ。</t>
         </is>
       </c>
-      <c r="J313" s="19" t="inlineStr">
+      <c r="J314" s="19" t="inlineStr">
         <is>
           <t>If you have a Potion of Restore Body or a Potion of Restore Mind,
 drinking one of those can restore your weakened attributes.</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Se você tiver uma Potion of Restore Body (Poção de Restauração do Corpo) ou uma Potion of Restore Mind (Poção de Restauração da Mente), beber uma delas pode restaurar seus atributos enfraquecidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H314" s="15" t="n">
+      <c r="K314" s="15" t="inlineStr">
+        <is>
+          <t>Se você tiver uma Poção de Restaurar Corpo ou uma Poção de Restaurar Mente,
+beber uma delas restaura seus atributos enfraquecidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H315" s="15" t="n">
         <v>64</v>
       </c>
-      <c r="I314" s="19" t="inlineStr">
+      <c r="I315" s="19" t="inlineStr">
         <is>
           <t>回復の手段がない時は、街にいる癒し手に頼めば
 治療費と引き換えに治してもらえるけど…</t>
         </is>
       </c>
-      <c r="J314" s="19" t="inlineStr">
+      <c r="J315" s="19" t="inlineStr">
         <is>
           <t>If you don't have a way to recover, you can ask a healer in town.
 It will cost you some money, but they can treat you...</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Se você não tiver uma maneira de se recuperar, pode pedir a um curandeiro da cidade.
-Isso lhe custará algum dinheiro, mas ele poderá tratá-lo…</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="32.8" customHeight="1" s="17">
-      <c r="H315" s="15" t="n">
+      <c r="K315" s="15" t="inlineStr">
+        <is>
+          <t>Se não tiver como recuperar, peça ajuda a um curandeiro na cidade.
+Vai custar algum dinheiro, mas eles tratam você...</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="32.8" customHeight="1" s="17">
+      <c r="H316" s="15" t="n">
         <v>65</v>
       </c>
-      <c r="I315" s="19" t="inlineStr">
+      <c r="I316" s="19" t="inlineStr">
         <is>
           <t>まあ、攻撃を受けないのが一番ね。
 近づくと厄介な敵には、遠隔から攻撃するといいわ。</t>
         </is>
       </c>
-      <c r="J315" s="19" t="inlineStr">
+      <c r="J316" s="19" t="inlineStr">
         <is>
           <t>Well, it's best not to get hit in the first place.
 For enemies that are troublesome up close,
 it's always better to attack them from a distance.</t>
         </is>
       </c>
-      <c r="K315" s="15" t="inlineStr">
-        <is>
-          <t>Bem, é melhor não ser atingido em primeiro lugar.
-Para inimigos que são problemáticos de perto,
-é sempre melhor atacá-los à distância.</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="12.8" customHeight="1" s="17">
-      <c r="B316" s="19" t="inlineStr">
+      <c r="K316" s="15" t="inlineStr">
+        <is>
+          <t>Bom, o melhor é nem ser atingido.
+Para inimigos chatos de perto,
+sempre é melhor atacar à distância.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="12.8" customHeight="1" s="17">
+      <c r="B317" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K316" s="15" t="n"/>
-    </row>
-    <row r="317" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K317" s="15" t="n"/>
+    </row>
     <row r="318" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A319" s="19" t="inlineStr">
+    <row r="319" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="320" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A320" s="19" t="inlineStr">
         <is>
           <t>fame</t>
         </is>
       </c>
     </row>
-    <row r="320" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H320" s="15" t="n">
+    <row r="321" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H321" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="I320" s="19" t="inlineStr">
+      <c r="I321" s="19" t="inlineStr">
         <is>
           <t>わあ、名声を獲得したのね！
 おめでと～！</t>
         </is>
       </c>
-      <c r="J320" s="25" t="inlineStr">
+      <c r="J321" s="25" t="inlineStr">
         <is>
           <t>Wow, you’ve gained fame!
 Congratulations!</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uau, você ganhou fama!  _x000D_
-Parabéns!  </t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H321" s="15" t="n">
+      <c r="K321" s="15" t="inlineStr">
+        <is>
+          <t>Nossa, você ganhou fama!
+Parabéns!</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H322" s="15" t="n">
         <v>54</v>
       </c>
-      <c r="I321" s="19" t="inlineStr">
+      <c r="I322" s="19" t="inlineStr">
         <is>
           <t>名声は、依頼を達成したり
 ネフィアを踏破することで獲得できるわ。</t>
         </is>
       </c>
-      <c r="J321" s="25" t="inlineStr">
+      <c r="J322" s="25" t="inlineStr">
         <is>
           <t>You can earn fame by completing quests
 and exploring Nefia.</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode ganhar fama completando missões  _x000D_
-e explorando Nefia.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H322" s="15" t="n">
+      <c r="K322" s="15" t="inlineStr">
+        <is>
+          <t>Você ganha fama completando missões
+e explorando Nefia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H323" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="I322" s="19" t="inlineStr">
+      <c r="I323" s="19" t="inlineStr">
         <is>
           <t>名声が上がると、より難易度の高い依頼を頼まれたり
 危険度の高いネフィアが出現するようになるの。</t>
         </is>
       </c>
-      <c r="J322" s="25" t="inlineStr">
+      <c r="J323" s="25" t="inlineStr">
         <is>
           <t>As your fame increases, you’ll be asked to take on more challenging quests,
 and more dangerous Nefia will appear.</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>À medida que sua fama aumenta, você será solicitado a participar de missões mais desafiadoras,
-e a Nefia, mais perigosa, aparecerá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="23.85" customFormat="1" customHeight="1" s="15">
-      <c r="H323" s="15" t="n">
+      <c r="K323" s="15" t="inlineStr">
+        <is>
+          <t>Conforme sua fama aumenta, pedem missões mais desafiadoras,
+e Nefias mais perigosas aparecem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="23.85" customFormat="1" customHeight="1" s="15">
+      <c r="H324" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I323" s="19" t="inlineStr">
+      <c r="I324" s="19" t="inlineStr">
         <is>
           <t>いっぱい名声を稼いで
 早く立派な冒険者になってね！</t>
         </is>
       </c>
-      <c r="J323" s="25" t="inlineStr">
+      <c r="J324" s="25" t="inlineStr">
         <is>
           <t>Earn lots of fame and
 become a renowned adventurer soon!</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Ganhe muita fama e 
-torne-se rapidamente um grande aventureiro!</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H324" s="15" t="n">
+      <c r="K324" s="15" t="inlineStr">
+        <is>
+          <t>Ganhe muita fama e
+vire logo um aventureiro renomado!</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H325" s="15" t="n">
         <v>57</v>
       </c>
-      <c r="I324" s="19" t="inlineStr">
+      <c r="I325" s="19" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="J324" s="19" t="inlineStr">
+      <c r="J325" s="19" t="inlineStr">
         <is>
           <t>...</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H325" s="15" t="n">
+      <c r="K325" s="15" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="H326" s="15" t="n">
         <v>58</v>
       </c>
-      <c r="I325" s="19" t="inlineStr">
+      <c r="I326" s="19" t="inlineStr">
         <is>
           <t>ちなみに…
 もし名声が高すぎて冒険がきつくなったら
 街の情報屋に名声を売るという手段もあるわ…</t>
         </is>
       </c>
-      <c r="J325" s="25" t="inlineStr">
+      <c r="J326" s="25" t="inlineStr">
         <is>
           <t>By the way...
 if your fame gets too high and the adventures become too tough,
 you can sell your fame to the town’s informant...</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A propósito...  _x000D_
-se sua fama ficar muito alta e as aventuras se tornarem difíceis demais,  _x000D_
-você pode vender sua fama para o informante da cidade...  </t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="12.8" customHeight="1" s="17">
-      <c r="H326" s="15" t="n">
+      <c r="K326" s="15" t="inlineStr">
+        <is>
+          <t>Aliás...
+se sua fama subir demais e as aventuras ficarem duras demais,
+você pode vender sua fama para o informante da cidade...</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="12.8" customHeight="1" s="17">
+      <c r="H327" s="15" t="n">
         <v>59</v>
       </c>
-      <c r="I326" s="19" t="inlineStr">
+      <c r="I327" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J326" s="25" t="inlineStr">
+      <c r="J327" s="25" t="inlineStr">
         <is>
           <t>Well then...</t>
         </is>
       </c>
-      <c r="K326" s="15" t="inlineStr">
-        <is>
-          <t>Então, bem…</t>
-        </is>
-      </c>
-    </row>
-    <row r="327" ht="12.8" customHeight="1" s="17">
-      <c r="B327" s="19" t="inlineStr">
+      <c r="K327" s="15" t="inlineStr">
+        <is>
+          <t>Pois então...</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="12.8" customHeight="1" s="17">
+      <c r="B328" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K327" s="15" t="n"/>
-    </row>
-    <row r="329" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K328" s="15" t="n"/>
+    </row>
     <row r="330" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A331" s="19" t="inlineStr">
+    <row r="331" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="332" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A332" s="19" t="inlineStr">
         <is>
           <t>sleep</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="H332" s="15" t="n">
+    <row r="333" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="H333" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="I332" s="19" t="inlineStr">
+      <c r="I333" s="19" t="inlineStr">
         <is>
           <t>疲れた顔してるけど大丈夫…？</t>
         </is>
       </c>
-      <c r="J332" s="25" t="inlineStr">
+      <c r="J333" s="25" t="inlineStr">
         <is>
           <t>You look tired, are you okay?</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Você parece cansado. Está bem?</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H333" s="15" t="n">
+      <c r="K333" s="15" t="inlineStr">
+        <is>
+          <t>Você parece cansado, está bem?</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H334" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="I333" s="19" t="inlineStr">
+      <c r="I334" s="19" t="inlineStr">
         <is>
           <t>疲れをとるには、ふかふかのベッドで
 ぐっすり眠るのが一番。</t>
         </is>
       </c>
-      <c r="J333" s="19" t="inlineStr">
+      <c r="J334" s="19" t="inlineStr">
         <is>
           <t>The best way to recover from fatigue is
 to get a good night's sleep in a comfy bed.</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>A melhor maneira de se recuperar da fadiga é
-ter uma boa noite de sono em uma cama confortável.</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H334" s="15" t="n">
+      <c r="K334" s="15" t="inlineStr">
+        <is>
+          <t>O melhor jeito de recuperar do cansaço é
+dormir uma noite inteira numa cama confortável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H335" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="I334" s="19" t="inlineStr">
+      <c r="I335" s="19" t="inlineStr">
         <is>
           <t>しっかり睡眠をとれば
 レシピを閃いたり、潜在能力が鍛えられたり
 夢で魔法を覚えられたり、いいことがあるかも。</t>
         </is>
       </c>
-      <c r="J334" s="19" t="inlineStr">
+      <c r="J335" s="19" t="inlineStr">
         <is>
           <t>When you get enough sleep,
 you might get new recipe ideas, train your potentials,
 or even learn magic in your dreams.</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Quando você dorme o suficiente, pode ter novas ideias de receitas, treinar seus talentos ou até mesmo aprender magia em seus sonhos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="35.05" customFormat="1" customHeight="1" s="15">
-      <c r="H335" s="15" t="n">
+      <c r="K335" s="15" t="inlineStr">
+        <is>
+          <t>Quando você dorme o suficiente,
+pode ter ideias de receitas novas, treinar seus potenciais,
+ou até aprender magia sonhando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="35.05" customFormat="1" customHeight="1" s="15">
+      <c r="H336" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="I335" s="19" t="inlineStr">
+      <c r="I336" s="19" t="inlineStr">
         <is>
           <t>まだベッドを作っていないなら
 「休憩」のアビリティを使うことで眠ることもできるわ。
 ベッドで眠るより効果はおちるけどね。</t>
         </is>
       </c>
-      <c r="J335" s="25" t="inlineStr">
+      <c r="J336" s="25" t="inlineStr">
         <is>
           <t>If you haven't made a bed yet,
 you can use the "Rest" ability to sleep.
 It's not as effective as sleeping in a bed, though.</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se você ainda não fez uma cama,  
-pode usar a habilidade "Descansar" para dormir.  
-Não é tão eficaz quanto dormir em uma cama, no entanto, mas serve.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H336" s="15" t="n">
+      <c r="K336" s="15" t="inlineStr">
+        <is>
+          <t>Se ainda não fez uma cama,
+pode usar a habilidade "Descansar" para dormir.
+Não é tão eficaz quanto dormir numa cama, porém.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H337" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="I336" s="19" t="inlineStr">
+      <c r="I337" s="19" t="inlineStr">
         <is>
           <t>休憩中は体力や魔力の自然回復量も上がるから
 戦いの後は休憩するのもありね。
@@ -7973,7 +8047,7 @@
 自然回復自体止まってしまうから気を付けて。</t>
         </is>
       </c>
-      <c r="J336" s="19" t="inlineStr">
+      <c r="J337" s="19" t="inlineStr">
         <is>
           <t>When resting, your natural recovery of health and magic power increases,
 so it's good to rest after a battle.
@@ -7981,127 +8055,130 @@
 natural recovery stops altogether.</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Ao descansar, sua recuperação natural de saúde e poder mágico aumenta, portanto, é bom descansar depois de uma batalha.
-Mas tome cuidado, pois se você estiver sobrecarregado ou faminto, a recuperação natural será interrompida completamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="22.35" customHeight="1" s="17">
-      <c r="H337" s="15" t="n">
+      <c r="K337" s="15" t="inlineStr">
+        <is>
+          <t>Descansando, sua recuperação natural de vida e mana aumenta,
+então é bom descansar depois de uma batalha.
+Só cuidado: se estiver exausto ou faminto,
+a recuperação natural para por completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="22.35" customHeight="1" s="17">
+      <c r="H338" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="I337" s="19" t="inlineStr">
+      <c r="I338" s="19" t="inlineStr">
         <is>
           <t>じゃあ、しっかり睡眠をとるのよ！</t>
         </is>
       </c>
-      <c r="J337" s="19" t="inlineStr">
+      <c r="J338" s="19" t="inlineStr">
         <is>
           <t>Okay that's it for now.
 Make sure to get plenty of sleep!</t>
         </is>
       </c>
-      <c r="K337" s="15" t="inlineStr">
-        <is>
-          <t>Por enquanto é isso.
-Não deixe de dormir bastante!</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="12.8" customHeight="1" s="17">
-      <c r="B338" s="19" t="inlineStr">
+      <c r="K338" s="15" t="inlineStr">
+        <is>
+          <t>Beleza, é isso por ora.
+Durma bastante, hein!</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="12.8" customHeight="1" s="17">
+      <c r="B339" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K338" s="15" t="n"/>
-    </row>
-    <row r="339" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+      <c r="K339" s="15" t="n"/>
+    </row>
     <row r="340" ht="12.8" customFormat="1" customHeight="1" s="15"/>
-    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15">
-      <c r="A341" s="19" t="inlineStr">
+    <row r="341" ht="12.8" customFormat="1" customHeight="1" s="15"/>
+    <row r="342" ht="12.8" customFormat="1" customHeight="1" s="15">
+      <c r="A342" s="19" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H342" s="15" t="n">
+    <row r="343" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H343" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I342" s="19" t="inlineStr">
+      <c r="I343" s="19" t="inlineStr">
         <is>
           <t>おーい、ちょっとまって。
 …走るなコラ！</t>
         </is>
       </c>
-      <c r="J342" s="19" t="inlineStr">
+      <c r="J343" s="19" t="inlineStr">
         <is>
           <t>Hey, wait a minute.
 ...don't... don't run!</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ei, espere um minuto.  
-E não, não corra!  </t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H343" s="15" t="n">
+      <c r="K343" s="15" t="inlineStr">
+        <is>
+          <t>Ei, espera um pouco.
+...não... não fuja!</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H344" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I343" s="19" t="inlineStr">
+      <c r="I344" s="19" t="inlineStr">
         <is>
           <t>はぁはぁ…コホン</t>
         </is>
       </c>
-      <c r="J343" s="19" t="inlineStr">
+      <c r="J344" s="19" t="inlineStr">
         <is>
           <t>*huff* *puff*
 ...*cough*</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">*huff* *puff*  
-...*cof*  </t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="32.8" customFormat="1" customHeight="1" s="15">
-      <c r="H344" s="15" t="n">
+      <c r="K344" s="15" t="inlineStr">
+        <is>
+          <t>*bafo* *ufa*
+...*cof*</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="32.8" customFormat="1" customHeight="1" s="15">
+      <c r="H345" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I344" s="19" t="inlineStr">
+      <c r="I345" s="19" t="inlineStr">
         <is>
           <t>キミが今いるのは「グローバルマップ」よ。
 ワールドマップでは大距離を移動できるかわりに
 時間がとても早く経過するの。</t>
         </is>
       </c>
-      <c r="J344" s="19" t="inlineStr">
+      <c r="J345" s="19" t="inlineStr">
         <is>
           <t>You are now in the "Global Map".
 In the global map, you can travel great distances
 but time also passes very quickly.</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Agora você está no “Mapa Global”.
-No Mapa Global, você pode viajar grandes distâncias, mas o tempo também passa muito rápido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H345" s="15" t="n">
+      <c r="K345" s="15" t="inlineStr">
+        <is>
+          <t>Você está no "Mapa Global".
+No mapa global, você viaja grandes distâncias,
+mas o tempo também passa muito rápido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H346" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I345" s="19" t="inlineStr">
+      <c r="I346" s="19" t="inlineStr">
         <is>
           <t>食料を十分に持っていないと
 すぐ餓死するから気をつけてね。
@@ -8109,25 +8186,26 @@
 毒にかかってる時に移動なんかしないこと！</t>
         </is>
       </c>
-      <c r="J345" s="19" t="inlineStr">
+      <c r="J346" s="19" t="inlineStr">
         <is>
           <t>You will starve to death if you don't have enough food
 and conditions such as poison progress rapidly.
 So be careful when you move.</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>Você morrerá de fome se não tiver comida suficiente, e doenças como o veneno progridem rapidamente.
-Portanto, tenha cuidado ao se deslocar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="43.25" customFormat="1" customHeight="1" s="15">
-      <c r="H346" s="15" t="n">
+      <c r="K346" s="15" t="inlineStr">
+        <is>
+          <t>Você morre de fome se não tiver comida suficiente
+e condições como veneno progridem rapidamente.
+Então cuidado ao se mover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="43.25" customFormat="1" customHeight="1" s="15">
+      <c r="H347" s="15" t="n">
         <v>212</v>
       </c>
-      <c r="I346" s="19" t="inlineStr">
+      <c r="I347" s="19" t="inlineStr">
         <is>
           <t>食べるものがなくてどうしようもない時は
 自分のいる場所をクリックしてみて。
@@ -8135,7 +8213,7 @@
 森や平野なら、野生の食材も豊富にあるはず。</t>
         </is>
       </c>
-      <c r="J346" s="19" t="inlineStr">
+      <c r="J347" s="19" t="inlineStr">
         <is>
           <t>When you have nothing to eat, try clicking on yourself.
 You’ll be able to enter an “Outdoor Map” corresponding
@@ -8143,42 +8221,43 @@
 If you’re in a forest or plains, there should be plenty of wild food available.</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>Se você estiver sem comida e sem opções, tente abrir o "Mapa Global".
-Você vai ver um mapa relativo ao seu local atual.
-Se estiver em uma floresta ou planície, você encontrará muitos alimentos selvagens.
-Se pelo menos estiver perto de uma, vá até lá.</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="22.35" customFormat="1" customHeight="1" s="15">
-      <c r="H347" s="15" t="n">
+      <c r="K347" s="15" t="inlineStr">
+        <is>
+          <t>Quando não tiver nada para comer, tente clicar em você mesmo.
+Você pode entrar num "Mapa Externo" correspondente
+ao terreno em que está.
+Se estiver numa floresta ou planície, deve haver comida selvagem de sobra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="22.35" customFormat="1" customHeight="1" s="15">
+      <c r="H348" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="I347" s="19" t="inlineStr">
+      <c r="I348" s="19" t="inlineStr">
         <is>
           <t>そうそう、グローバルマップを移動していると
 モンスターに襲撃されることがあるわ。</t>
         </is>
       </c>
-      <c r="J347" s="19" t="inlineStr">
+      <c r="J348" s="19" t="inlineStr">
         <is>
           <t>Oh, and when you're traveling on the global map
 you might get attacked by monsters.</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Ah, e quando você estiver viajando no mapa global, poderá ser atacado por monstros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
-      <c r="H348" s="15" t="n">
+      <c r="K348" s="15" t="inlineStr">
+        <is>
+          <t>Ah, e quando estiver viajando no mapa global,
+você pode ser atacado por monstros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="74.59999999999999" customFormat="1" customHeight="1" s="15">
+      <c r="H349" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="I348" s="19" t="inlineStr">
+      <c r="I349" s="19" t="inlineStr">
         <is>
           <t>右手に街道が見えるでしょ？
 街道の上は襲撃が少なくて比較的安全。
@@ -8186,7 +8265,7 @@
 駆け出しのうちは、街道を利用するといいわ。</t>
         </is>
       </c>
-      <c r="J348" s="19" t="inlineStr">
+      <c r="J349" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">See that road to your right?
 Attacks are less frequent on the road
@@ -8195,89 +8274,91 @@
 So, for beginners, sticking to the road is a good idea. </t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Está vendo a estrada da cidade à sua direita?
-A estrada é relativamente segura, com menos ataques.
-Quanto mais você se afastar da estrada, maior será a probabilidade de encontrar inimigos mais fortes, portanto, quando estiver começando, vá pela estrada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="12.8" customHeight="1" s="17">
-      <c r="H349" s="15" t="n">
+      <c r="K349" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vê aquela estrada à sua direita?
+Os ataques são menos frequentes na estrada
+e quanto mais longe dela você se afasta,
+maior a chance de topar com inimigos fortes.
+Então, para iniciantes, ficar na estrada é uma boa ideia. </t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="12.8" customHeight="1" s="17">
+      <c r="H350" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="I349" s="19" t="inlineStr">
+      <c r="I350" s="19" t="inlineStr">
         <is>
           <t>それでは…</t>
         </is>
       </c>
-      <c r="J349" s="25" t="inlineStr">
+      <c r="J350" s="25" t="inlineStr">
         <is>
           <t>Well then...</t>
         </is>
       </c>
-      <c r="K349" s="15" t="inlineStr">
-        <is>
-          <t>Então, bem…</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="12.8" customHeight="1" s="17">
-      <c r="B350" s="19" t="inlineStr">
+      <c r="K350" s="15" t="inlineStr">
+        <is>
+          <t>Pois então...</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="12.8" customHeight="1" s="17">
+      <c r="B351" s="19" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="K350" s="15" t="n"/>
-    </row>
-    <row r="352" ht="12.8" customHeight="1" s="17">
-      <c r="A352" s="15" t="inlineStr">
+      <c r="K351" s="15" t="n"/>
+    </row>
+    <row r="353" ht="12.8" customHeight="1" s="17">
+      <c r="A353" s="15" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
     </row>
-    <row r="353" ht="12.8" customHeight="1" s="17">
-      <c r="D353" s="15" t="inlineStr">
+    <row r="354" ht="12.8" customHeight="1" s="17">
+      <c r="D354" s="15" t="inlineStr">
         <is>
           <t>hideUI</t>
         </is>
       </c>
-      <c r="E353" s="15" t="inlineStr">
+      <c r="E354" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="354" ht="22.35" customHeight="1" s="17">
-      <c r="H354" s="15" t="n">
+    <row r="355" ht="22.35" customHeight="1" s="17">
+      <c r="H355" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="I354" s="19" t="inlineStr">
+      <c r="I355" s="19" t="inlineStr">
         <is>
           <t>そうそう
 Demoはこれでおしまいよ。</t>
         </is>
       </c>
-      <c r="J354" s="19" t="inlineStr">
+      <c r="J355" s="19" t="inlineStr">
         <is>
           <t>Oh yes.
 This is the end of the Demo.</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh, sim.  _x000D_
-Este é o fim da Demo.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="43.25" customHeight="1" s="17">
-      <c r="H355" s="15" t="n">
+      <c r="K355" s="15" t="inlineStr">
+        <is>
+          <t>Ah, sim.
+Este é o fim da Demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="43.25" customHeight="1" s="17">
+      <c r="H356" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I355" s="19" t="inlineStr">
+      <c r="I356" s="19" t="inlineStr">
         <is>
           <t>この先の街や色々な場所を訪れることもできるけど
 まだ未実装の部分も多いし
@@ -8285,7 +8366,7 @@
 あまりオススメはしないわ。</t>
         </is>
       </c>
-      <c r="J355" s="19" t="inlineStr">
+      <c r="J356" s="19" t="inlineStr">
         <is>
           <t>You can still visit cities and places down the road
 but I don't recommend it as there are
@@ -8293,93 +8374,65 @@
 and it will spoil the fun and surprises later on.</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você ainda pode visitar cidades e lugares adiante,  
-mas não recomendo, pois há  muitos aspectos não implementados e isso estragaria a diversão e as surpresas futuras.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="22.35" customHeight="1" s="17">
-      <c r="B356" s="15" t="inlineStr">
+      <c r="K356" s="15" t="inlineStr">
+        <is>
+          <t>Você ainda pode visitar cidades e lugares adiante na estrada,
+mas não recomendo: ainda há muitos aspectos não implementados,
+e estragaria a diversão
+e as surpresas futuras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="22.35" customHeight="1" s="17">
+      <c r="B357" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="H356" s="15" t="n">
+      <c r="H357" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I356" s="19" t="inlineStr">
+      <c r="I357" s="19" t="inlineStr">
         <is>
           <t>少し観光したら
 そっとゲームを閉じていってね。</t>
         </is>
       </c>
-      <c r="J356" s="19" t="inlineStr">
+      <c r="J357" s="19" t="inlineStr">
         <is>
           <t>After a little sightseeing
 please close the game gently.</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Depois de um pequeno passeio,  
-por favor, feche o jogo com cuidado.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="359" ht="12.8" customHeight="1" s="17">
-      <c r="A359" s="15" t="inlineStr">
+      <c r="K357" s="15" t="inlineStr">
+        <is>
+          <t>Depois de um passeiozinho,
+por favor feche o jogo com carinho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="12.8" customHeight="1" s="17">
+      <c r="A360" s="15" t="inlineStr">
         <is>
           <t>9-1</t>
         </is>
       </c>
-      <c r="H359" s="15" t="n">
+      <c r="H360" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="I359" s="15" t="inlineStr">
+      <c r="I360" s="15" t="inlineStr">
         <is>
           <t>なになに？</t>
         </is>
       </c>
-      <c r="J359" s="15" t="inlineStr">
+      <c r="J360" s="15" t="inlineStr">
         <is>
           <t>What?</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O quê?  </t>
-        </is>
-      </c>
-    </row>
-    <row r="360" ht="12.8" customHeight="1" s="17">
-      <c r="B360" s="15" t="inlineStr">
-        <is>
-          <t>9-2</t>
-        </is>
-      </c>
-      <c r="D360" s="15" t="inlineStr">
-        <is>
-          <t>choice</t>
-        </is>
-      </c>
-      <c r="H360" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I360" s="15" t="inlineStr">
-        <is>
-          <t>明日の天気は？</t>
-        </is>
-      </c>
-      <c r="J360" s="15" t="inlineStr">
-        <is>
-          <t>What will the weather be tomorrow?</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>Como estará o tempo amanhã?</t>
+      <c r="K360" s="15" t="inlineStr">
+        <is>
+          <t>Que?</t>
         </is>
       </c>
     </row>
@@ -8395,28 +8448,28 @@
         </is>
       </c>
       <c r="H361" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I361" s="15" t="inlineStr">
         <is>
-          <t>今日の運勢は？</t>
+          <t>明日の天気は？</t>
         </is>
       </c>
       <c r="J361" s="15" t="inlineStr">
         <is>
-          <t>How is my fortune today?</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qual é a minha sorte hoje?  </t>
+          <t>What will the weather be tomorrow?</t>
+        </is>
+      </c>
+      <c r="K361" s="15" t="inlineStr">
+        <is>
+          <t>Como estará o tempo amanhã?</t>
         </is>
       </c>
     </row>
     <row r="362" ht="12.8" customHeight="1" s="17">
       <c r="B362" s="15" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="D362" s="15" t="inlineStr">
@@ -8425,97 +8478,127 @@
         </is>
       </c>
       <c r="H362" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I362" s="15" t="inlineStr">
         <is>
-          <t>なんでもない</t>
+          <t>今日の運勢は？</t>
         </is>
       </c>
       <c r="J362" s="15" t="inlineStr">
         <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nada  </t>
+          <t>How is my fortune today?</t>
+        </is>
+      </c>
+      <c r="K362" s="15" t="inlineStr">
+        <is>
+          <t>Como está minha sorte hoje?</t>
         </is>
       </c>
     </row>
     <row r="363" ht="12.8" customHeight="1" s="17">
       <c r="B363" s="15" t="inlineStr">
         <is>
+          <t>9-3</t>
+        </is>
+      </c>
+      <c r="D363" s="15" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="H363" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I363" s="15" t="inlineStr">
+        <is>
+          <t>なんでもない</t>
+        </is>
+      </c>
+      <c r="J363" s="15" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="K363" s="15" t="inlineStr">
+        <is>
+          <t>Nada</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="12.8" customHeight="1" s="17">
+      <c r="B364" s="15" t="inlineStr">
+        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="D363" s="15" t="inlineStr">
+      <c r="D364" s="15" t="inlineStr">
         <is>
           <t>cancel</t>
         </is>
       </c>
     </row>
-    <row r="367" ht="12.8" customHeight="1" s="17">
-      <c r="A367" s="15" t="inlineStr">
+    <row r="368" ht="12.8" customHeight="1" s="17">
+      <c r="A368" s="15" t="inlineStr">
         <is>
           <t>9-2</t>
         </is>
       </c>
-      <c r="H367" s="15" t="n">
+      <c r="H368" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I367" s="15" t="inlineStr">
+      <c r="I368" s="15" t="inlineStr">
         <is>
           <t>…さあ？</t>
         </is>
       </c>
-      <c r="J367" s="15" t="inlineStr">
+      <c r="J368" s="15" t="inlineStr">
         <is>
           <t>...who knows?</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>... E então?</t>
-        </is>
-      </c>
-    </row>
-    <row r="368" ht="12.8" customHeight="1" s="17">
-      <c r="B368" s="15" t="inlineStr">
+      <c r="K368" s="15" t="inlineStr">
+        <is>
+          <t>...quem sabe?</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="12.8" customHeight="1" s="17">
+      <c r="B369" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="371" ht="12.8" customHeight="1" s="17">
-      <c r="A371" s="15" t="inlineStr">
+    <row r="372" ht="12.8" customHeight="1" s="17">
+      <c r="A372" s="15" t="inlineStr">
         <is>
           <t>9-3</t>
         </is>
       </c>
     </row>
-    <row r="372" ht="12.8" customHeight="1" s="17">
-      <c r="H372" s="15" t="n">
+    <row r="373" ht="12.8" customHeight="1" s="17">
+      <c r="H373" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="I372" s="15" t="inlineStr">
+      <c r="I373" s="15" t="inlineStr">
         <is>
           <t>用事もないのに呼ばないで。</t>
         </is>
       </c>
-      <c r="J372" s="15" t="inlineStr">
+      <c r="J373" s="15" t="inlineStr">
         <is>
           <t>Don't disturb me for nothing.</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não me incomode por nada.  </t>
-        </is>
-      </c>
-    </row>
-    <row r="373" ht="12.8" customHeight="1" s="17">
-      <c r="B373" s="15" t="inlineStr">
+      <c r="K373" s="15" t="inlineStr">
+        <is>
+          <t>Não me perturbe à toa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="12.8" customHeight="1" s="17">
+      <c r="B374" s="15" t="inlineStr">
         <is>
           <t>end</t>
         </is>
